--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ligue 1 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83C73406-FD95-423D-84F7-7691725F152B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3926C337-2C96-44EC-BE5B-2D1F9EAB0C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="596" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="140">
   <si>
     <t>date</t>
   </si>
@@ -451,6 +451,15 @@
   <si>
     <t>Sun 20 September, 20:45</t>
   </si>
+  <si>
+    <t>Fri 9 October, 20:45</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 17:15</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -507,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -523,6 +532,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ45"/>
+  <dimension ref="B1:CJ51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -1442,7 +1454,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H45" si="0">100-G3</f>
+        <f t="shared" ref="H3:H51" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -12771,6 +12783,1590 @@
         <v>1</v>
       </c>
       <c r="CJ45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>48</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="I46">
+        <v>1.34</v>
+      </c>
+      <c r="J46">
+        <v>1.04</v>
+      </c>
+      <c r="K46">
+        <v>15</v>
+      </c>
+      <c r="L46">
+        <v>13</v>
+      </c>
+      <c r="M46">
+        <v>7</v>
+      </c>
+      <c r="N46">
+        <v>5</v>
+      </c>
+      <c r="O46">
+        <v>2</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <v>386</v>
+      </c>
+      <c r="T46">
+        <v>414</v>
+      </c>
+      <c r="U46">
+        <v>13</v>
+      </c>
+      <c r="V46">
+        <v>12</v>
+      </c>
+      <c r="W46">
+        <v>7</v>
+      </c>
+      <c r="X46">
+        <v>4</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA46">
+        <v>7</v>
+      </c>
+      <c r="AB46">
+        <v>5</v>
+      </c>
+      <c r="AC46">
+        <v>1</v>
+      </c>
+      <c r="AD46">
+        <v>3</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>12</v>
+      </c>
+      <c r="AH46">
+        <v>9</v>
+      </c>
+      <c r="AI46">
+        <v>3</v>
+      </c>
+      <c r="AJ46">
+        <v>4</v>
+      </c>
+      <c r="AK46">
+        <v>0.8</v>
+      </c>
+      <c r="AL46">
+        <v>0.87</v>
+      </c>
+      <c r="AM46">
+        <v>0.54</v>
+      </c>
+      <c r="AN46">
+        <v>0.16</v>
+      </c>
+      <c r="AO46">
+        <v>1.34</v>
+      </c>
+      <c r="AP46">
+        <v>1.04</v>
+      </c>
+      <c r="AQ46">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AR46">
+        <v>1.48</v>
+      </c>
+      <c r="AS46">
+        <v>454</v>
+      </c>
+      <c r="AT46">
+        <v>488</v>
+      </c>
+      <c r="AU46">
+        <v>251</v>
+      </c>
+      <c r="AV46">
+        <v>221</v>
+      </c>
+      <c r="AW46">
+        <v>135</v>
+      </c>
+      <c r="AX46">
+        <v>193</v>
+      </c>
+      <c r="AY46">
+        <v>21</v>
+      </c>
+      <c r="AZ46">
+        <v>23</v>
+      </c>
+      <c r="BA46">
+        <v>6</v>
+      </c>
+      <c r="BB46">
+        <v>7</v>
+      </c>
+      <c r="BC46">
+        <v>19</v>
+      </c>
+      <c r="BD46">
+        <v>22</v>
+      </c>
+      <c r="BE46">
+        <v>28</v>
+      </c>
+      <c r="BF46">
+        <v>23</v>
+      </c>
+      <c r="BG46">
+        <v>1</v>
+      </c>
+      <c r="BH46">
+        <v>1</v>
+      </c>
+      <c r="BI46" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ46" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK46">
+        <v>20</v>
+      </c>
+      <c r="BL46">
+        <v>10</v>
+      </c>
+      <c r="BM46">
+        <v>9</v>
+      </c>
+      <c r="BN46">
+        <v>5</v>
+      </c>
+      <c r="BO46">
+        <v>3</v>
+      </c>
+      <c r="BP46">
+        <v>1</v>
+      </c>
+      <c r="BQ46">
+        <v>27</v>
+      </c>
+      <c r="BR46">
+        <v>23</v>
+      </c>
+      <c r="BS46">
+        <v>4</v>
+      </c>
+      <c r="BT46">
+        <v>5</v>
+      </c>
+      <c r="BU46" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV46" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW46">
+        <v>48</v>
+      </c>
+      <c r="BX46">
+        <v>39</v>
+      </c>
+      <c r="BY46">
+        <v>37</v>
+      </c>
+      <c r="BZ46">
+        <v>30</v>
+      </c>
+      <c r="CA46">
+        <v>11</v>
+      </c>
+      <c r="CB46">
+        <v>9</v>
+      </c>
+      <c r="CC46">
+        <v>6</v>
+      </c>
+      <c r="CD46">
+        <v>7</v>
+      </c>
+      <c r="CE46" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF46" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG46">
+        <v>1</v>
+      </c>
+      <c r="CH46">
+        <v>1</v>
+      </c>
+      <c r="CI46">
+        <v>1</v>
+      </c>
+      <c r="CJ46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>47</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="I47">
+        <v>1.19</v>
+      </c>
+      <c r="J47">
+        <v>1.3</v>
+      </c>
+      <c r="K47">
+        <v>5</v>
+      </c>
+      <c r="L47">
+        <v>17</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>2</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>344</v>
+      </c>
+      <c r="T47">
+        <v>380</v>
+      </c>
+      <c r="U47">
+        <v>17</v>
+      </c>
+      <c r="V47">
+        <v>12</v>
+      </c>
+      <c r="W47">
+        <v>4</v>
+      </c>
+      <c r="X47">
+        <v>5</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA47">
+        <v>4</v>
+      </c>
+      <c r="AB47">
+        <v>10</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>5</v>
+      </c>
+      <c r="AE47">
+        <v>1</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>3</v>
+      </c>
+      <c r="AH47">
+        <v>9</v>
+      </c>
+      <c r="AI47">
+        <v>2</v>
+      </c>
+      <c r="AJ47">
+        <v>8</v>
+      </c>
+      <c r="AK47">
+        <v>0.75</v>
+      </c>
+      <c r="AL47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AM47">
+        <v>0.44</v>
+      </c>
+      <c r="AN47">
+        <v>0.2</v>
+      </c>
+      <c r="AO47">
+        <v>1.19</v>
+      </c>
+      <c r="AP47">
+        <v>1.3</v>
+      </c>
+      <c r="AQ47">
+        <v>0.87</v>
+      </c>
+      <c r="AR47">
+        <v>0.05</v>
+      </c>
+      <c r="AS47">
+        <v>409</v>
+      </c>
+      <c r="AT47">
+        <v>449</v>
+      </c>
+      <c r="AU47">
+        <v>207</v>
+      </c>
+      <c r="AV47">
+        <v>198</v>
+      </c>
+      <c r="AW47">
+        <v>137</v>
+      </c>
+      <c r="AX47">
+        <v>182</v>
+      </c>
+      <c r="AY47">
+        <v>30</v>
+      </c>
+      <c r="AZ47">
+        <v>21</v>
+      </c>
+      <c r="BA47">
+        <v>2</v>
+      </c>
+      <c r="BB47">
+        <v>9</v>
+      </c>
+      <c r="BC47">
+        <v>17</v>
+      </c>
+      <c r="BD47">
+        <v>21</v>
+      </c>
+      <c r="BE47">
+        <v>11</v>
+      </c>
+      <c r="BF47">
+        <v>18</v>
+      </c>
+      <c r="BG47">
+        <v>4</v>
+      </c>
+      <c r="BH47">
+        <v>1</v>
+      </c>
+      <c r="BI47" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ47" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK47">
+        <v>24</v>
+      </c>
+      <c r="BL47">
+        <v>23</v>
+      </c>
+      <c r="BM47">
+        <v>7</v>
+      </c>
+      <c r="BN47">
+        <v>8</v>
+      </c>
+      <c r="BO47">
+        <v>5</v>
+      </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
+      <c r="BQ47">
+        <v>24</v>
+      </c>
+      <c r="BR47">
+        <v>10</v>
+      </c>
+      <c r="BS47">
+        <v>2</v>
+      </c>
+      <c r="BT47">
+        <v>0</v>
+      </c>
+      <c r="BU47" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV47" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW47">
+        <v>45</v>
+      </c>
+      <c r="BX47">
+        <v>58</v>
+      </c>
+      <c r="BY47">
+        <v>38</v>
+      </c>
+      <c r="BZ47">
+        <v>47</v>
+      </c>
+      <c r="CA47">
+        <v>7</v>
+      </c>
+      <c r="CB47">
+        <v>11</v>
+      </c>
+      <c r="CC47">
+        <v>3</v>
+      </c>
+      <c r="CD47">
+        <v>7</v>
+      </c>
+      <c r="CE47" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF47" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG47">
+        <v>2</v>
+      </c>
+      <c r="CH47">
+        <v>2</v>
+      </c>
+      <c r="CI47">
+        <v>0</v>
+      </c>
+      <c r="CJ47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>54</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I48">
+        <v>3.71</v>
+      </c>
+      <c r="J48">
+        <v>1.39</v>
+      </c>
+      <c r="K48">
+        <v>19</v>
+      </c>
+      <c r="L48">
+        <v>9</v>
+      </c>
+      <c r="M48">
+        <v>9</v>
+      </c>
+      <c r="N48">
+        <v>3</v>
+      </c>
+      <c r="O48">
+        <v>8</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <v>3</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>467</v>
+      </c>
+      <c r="T48">
+        <v>363</v>
+      </c>
+      <c r="U48">
+        <v>5</v>
+      </c>
+      <c r="V48">
+        <v>11</v>
+      </c>
+      <c r="W48">
+        <v>4</v>
+      </c>
+      <c r="X48">
+        <v>5</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA48">
+        <v>7</v>
+      </c>
+      <c r="AB48">
+        <v>4</v>
+      </c>
+      <c r="AC48">
+        <v>3</v>
+      </c>
+      <c r="AD48">
+        <v>2</v>
+      </c>
+      <c r="AE48">
+        <v>1</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>12</v>
+      </c>
+      <c r="AH48">
+        <v>8</v>
+      </c>
+      <c r="AI48">
+        <v>7</v>
+      </c>
+      <c r="AJ48">
+        <v>1</v>
+      </c>
+      <c r="AK48">
+        <v>2.13</v>
+      </c>
+      <c r="AL48">
+        <v>1.06</v>
+      </c>
+      <c r="AM48">
+        <v>0.79</v>
+      </c>
+      <c r="AN48">
+        <v>0.33</v>
+      </c>
+      <c r="AO48">
+        <v>2.92</v>
+      </c>
+      <c r="AP48">
+        <v>1.39</v>
+      </c>
+      <c r="AQ48">
+        <v>5.7</v>
+      </c>
+      <c r="AR48">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS48">
+        <v>530</v>
+      </c>
+      <c r="AT48">
+        <v>431</v>
+      </c>
+      <c r="AU48">
+        <v>276</v>
+      </c>
+      <c r="AV48">
+        <v>222</v>
+      </c>
+      <c r="AW48">
+        <v>191</v>
+      </c>
+      <c r="AX48">
+        <v>141</v>
+      </c>
+      <c r="AY48">
+        <v>32</v>
+      </c>
+      <c r="AZ48">
+        <v>33</v>
+      </c>
+      <c r="BA48">
+        <v>6</v>
+      </c>
+      <c r="BB48">
+        <v>8</v>
+      </c>
+      <c r="BC48">
+        <v>19</v>
+      </c>
+      <c r="BD48">
+        <v>10</v>
+      </c>
+      <c r="BE48">
+        <v>39</v>
+      </c>
+      <c r="BF48">
+        <v>16</v>
+      </c>
+      <c r="BG48">
+        <v>1</v>
+      </c>
+      <c r="BH48">
+        <v>0</v>
+      </c>
+      <c r="BI48" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ48" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK48">
+        <v>8</v>
+      </c>
+      <c r="BL48">
+        <v>18</v>
+      </c>
+      <c r="BM48">
+        <v>11</v>
+      </c>
+      <c r="BN48">
+        <v>4</v>
+      </c>
+      <c r="BO48">
+        <v>2</v>
+      </c>
+      <c r="BP48">
+        <v>2</v>
+      </c>
+      <c r="BQ48">
+        <v>14</v>
+      </c>
+      <c r="BR48">
+        <v>13</v>
+      </c>
+      <c r="BS48">
+        <v>2</v>
+      </c>
+      <c r="BT48">
+        <v>4</v>
+      </c>
+      <c r="BU48" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV48" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW48">
+        <v>45</v>
+      </c>
+      <c r="BX48">
+        <v>37</v>
+      </c>
+      <c r="BY48">
+        <v>28</v>
+      </c>
+      <c r="BZ48">
+        <v>29</v>
+      </c>
+      <c r="CA48">
+        <v>17</v>
+      </c>
+      <c r="CB48">
+        <v>8</v>
+      </c>
+      <c r="CC48">
+        <v>9</v>
+      </c>
+      <c r="CD48">
+        <v>6</v>
+      </c>
+      <c r="CE48" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF48" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG48">
+        <v>1</v>
+      </c>
+      <c r="CH48">
+        <v>1</v>
+      </c>
+      <c r="CI48">
+        <v>0</v>
+      </c>
+      <c r="CJ48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>40</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I49">
+        <v>0.49</v>
+      </c>
+      <c r="J49">
+        <v>0.69</v>
+      </c>
+      <c r="K49">
+        <v>8</v>
+      </c>
+      <c r="L49">
+        <v>16</v>
+      </c>
+      <c r="M49">
+        <v>5</v>
+      </c>
+      <c r="N49">
+        <v>3</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>400</v>
+      </c>
+      <c r="T49">
+        <v>634</v>
+      </c>
+      <c r="U49">
+        <v>9</v>
+      </c>
+      <c r="V49">
+        <v>13</v>
+      </c>
+      <c r="W49">
+        <v>3</v>
+      </c>
+      <c r="X49">
+        <v>9</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA49">
+        <v>3</v>
+      </c>
+      <c r="AB49">
+        <v>4</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>9</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>6</v>
+      </c>
+      <c r="AH49">
+        <v>8</v>
+      </c>
+      <c r="AI49">
+        <v>2</v>
+      </c>
+      <c r="AJ49">
+        <v>8</v>
+      </c>
+      <c r="AK49">
+        <v>0.33</v>
+      </c>
+      <c r="AL49">
+        <v>0.39</v>
+      </c>
+      <c r="AM49">
+        <v>0.16</v>
+      </c>
+      <c r="AN49">
+        <v>0.3</v>
+      </c>
+      <c r="AO49">
+        <v>0.49</v>
+      </c>
+      <c r="AP49">
+        <v>0.69</v>
+      </c>
+      <c r="AQ49">
+        <v>1.22</v>
+      </c>
+      <c r="AR49">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS49">
+        <v>468</v>
+      </c>
+      <c r="AT49">
+        <v>702</v>
+      </c>
+      <c r="AU49">
+        <v>279</v>
+      </c>
+      <c r="AV49">
+        <v>201</v>
+      </c>
+      <c r="AW49">
+        <v>121</v>
+      </c>
+      <c r="AX49">
+        <v>433</v>
+      </c>
+      <c r="AY49">
+        <v>19</v>
+      </c>
+      <c r="AZ49">
+        <v>19</v>
+      </c>
+      <c r="BA49">
+        <v>2</v>
+      </c>
+      <c r="BB49">
+        <v>4</v>
+      </c>
+      <c r="BC49">
+        <v>6</v>
+      </c>
+      <c r="BD49">
+        <v>13</v>
+      </c>
+      <c r="BE49">
+        <v>14</v>
+      </c>
+      <c r="BF49">
+        <v>25</v>
+      </c>
+      <c r="BG49">
+        <v>0</v>
+      </c>
+      <c r="BH49">
+        <v>3</v>
+      </c>
+      <c r="BI49" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ49" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK49">
+        <v>13</v>
+      </c>
+      <c r="BL49">
+        <v>12</v>
+      </c>
+      <c r="BM49">
+        <v>11</v>
+      </c>
+      <c r="BN49">
+        <v>11</v>
+      </c>
+      <c r="BO49">
+        <v>8</v>
+      </c>
+      <c r="BP49">
+        <v>1</v>
+      </c>
+      <c r="BQ49">
+        <v>37</v>
+      </c>
+      <c r="BR49">
+        <v>16</v>
+      </c>
+      <c r="BS49">
+        <v>3</v>
+      </c>
+      <c r="BT49">
+        <v>3</v>
+      </c>
+      <c r="BU49" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV49" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW49">
+        <v>54</v>
+      </c>
+      <c r="BX49">
+        <v>37</v>
+      </c>
+      <c r="BY49">
+        <v>36</v>
+      </c>
+      <c r="BZ49">
+        <v>25</v>
+      </c>
+      <c r="CA49">
+        <v>18</v>
+      </c>
+      <c r="CB49">
+        <v>12</v>
+      </c>
+      <c r="CC49">
+        <v>10</v>
+      </c>
+      <c r="CD49">
+        <v>4</v>
+      </c>
+      <c r="CE49" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF49" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG49">
+        <v>1</v>
+      </c>
+      <c r="CH49">
+        <v>5</v>
+      </c>
+      <c r="CI49">
+        <v>0</v>
+      </c>
+      <c r="CJ49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>58</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I50">
+        <v>1.06</v>
+      </c>
+      <c r="J50">
+        <v>1.37</v>
+      </c>
+      <c r="K50">
+        <v>16</v>
+      </c>
+      <c r="L50">
+        <v>9</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50">
+        <v>4</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
+        <v>2</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>574</v>
+      </c>
+      <c r="T50">
+        <v>407</v>
+      </c>
+      <c r="U50">
+        <v>10</v>
+      </c>
+      <c r="V50">
+        <v>16</v>
+      </c>
+      <c r="W50">
+        <v>4</v>
+      </c>
+      <c r="X50">
+        <v>4</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA50">
+        <v>8</v>
+      </c>
+      <c r="AB50">
+        <v>3</v>
+      </c>
+      <c r="AC50">
+        <v>4</v>
+      </c>
+      <c r="AD50">
+        <v>2</v>
+      </c>
+      <c r="AE50">
+        <v>2</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>11</v>
+      </c>
+      <c r="AH50">
+        <v>5</v>
+      </c>
+      <c r="AI50">
+        <v>5</v>
+      </c>
+      <c r="AJ50">
+        <v>4</v>
+      </c>
+      <c r="AK50">
+        <v>0.78</v>
+      </c>
+      <c r="AL50">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AM50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN50">
+        <v>0</v>
+      </c>
+      <c r="AO50">
+        <v>1.06</v>
+      </c>
+      <c r="AP50">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AQ50">
+        <v>1.32</v>
+      </c>
+      <c r="AR50">
+        <v>2.08</v>
+      </c>
+      <c r="AS50">
+        <v>645</v>
+      </c>
+      <c r="AT50">
+        <v>466</v>
+      </c>
+      <c r="AU50">
+        <v>241</v>
+      </c>
+      <c r="AV50">
+        <v>262</v>
+      </c>
+      <c r="AW50">
+        <v>333</v>
+      </c>
+      <c r="AX50">
+        <v>145</v>
+      </c>
+      <c r="AY50">
+        <v>30</v>
+      </c>
+      <c r="AZ50">
+        <v>17</v>
+      </c>
+      <c r="BA50">
+        <v>4</v>
+      </c>
+      <c r="BB50">
+        <v>1</v>
+      </c>
+      <c r="BC50">
+        <v>16</v>
+      </c>
+      <c r="BD50">
+        <v>13</v>
+      </c>
+      <c r="BE50">
+        <v>22</v>
+      </c>
+      <c r="BF50">
+        <v>15</v>
+      </c>
+      <c r="BG50">
+        <v>0</v>
+      </c>
+      <c r="BH50">
+        <v>1</v>
+      </c>
+      <c r="BI50" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ50" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK50">
+        <v>21</v>
+      </c>
+      <c r="BL50">
+        <v>19</v>
+      </c>
+      <c r="BM50">
+        <v>8</v>
+      </c>
+      <c r="BN50">
+        <v>8</v>
+      </c>
+      <c r="BO50">
+        <v>2</v>
+      </c>
+      <c r="BP50">
+        <v>4</v>
+      </c>
+      <c r="BQ50">
+        <v>7</v>
+      </c>
+      <c r="BR50">
+        <v>37</v>
+      </c>
+      <c r="BS50">
+        <v>2</v>
+      </c>
+      <c r="BT50">
+        <v>2</v>
+      </c>
+      <c r="BU50" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV50" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW50">
+        <v>52</v>
+      </c>
+      <c r="BX50">
+        <v>40</v>
+      </c>
+      <c r="BY50">
+        <v>46</v>
+      </c>
+      <c r="BZ50">
+        <v>36</v>
+      </c>
+      <c r="CA50">
+        <v>6</v>
+      </c>
+      <c r="CB50">
+        <v>4</v>
+      </c>
+      <c r="CC50">
+        <v>10</v>
+      </c>
+      <c r="CD50">
+        <v>7</v>
+      </c>
+      <c r="CE50" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF50" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG50">
+        <v>2</v>
+      </c>
+      <c r="CH50">
+        <v>2</v>
+      </c>
+      <c r="CI50">
+        <v>0</v>
+      </c>
+      <c r="CJ50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>73</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="I51">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J51">
+        <v>1.55</v>
+      </c>
+      <c r="K51">
+        <v>22</v>
+      </c>
+      <c r="L51">
+        <v>11</v>
+      </c>
+      <c r="M51">
+        <v>8</v>
+      </c>
+      <c r="N51">
+        <v>3</v>
+      </c>
+      <c r="O51">
+        <v>7</v>
+      </c>
+      <c r="P51">
+        <v>4</v>
+      </c>
+      <c r="Q51">
+        <v>5</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="S51">
+        <v>626</v>
+      </c>
+      <c r="T51">
+        <v>181</v>
+      </c>
+      <c r="U51">
+        <v>3</v>
+      </c>
+      <c r="V51">
+        <v>17</v>
+      </c>
+      <c r="W51">
+        <v>4</v>
+      </c>
+      <c r="X51">
+        <v>4</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA51">
+        <v>8</v>
+      </c>
+      <c r="AB51">
+        <v>7</v>
+      </c>
+      <c r="AC51">
+        <v>6</v>
+      </c>
+      <c r="AD51">
+        <v>1</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>1</v>
+      </c>
+      <c r="AG51">
+        <v>13</v>
+      </c>
+      <c r="AH51">
+        <v>7</v>
+      </c>
+      <c r="AI51">
+        <v>9</v>
+      </c>
+      <c r="AJ51">
+        <v>4</v>
+      </c>
+      <c r="AK51">
+        <v>1.58</v>
+      </c>
+      <c r="AL51">
+        <v>0.86</v>
+      </c>
+      <c r="AM51">
+        <v>0.94</v>
+      </c>
+      <c r="AN51">
+        <v>0.69</v>
+      </c>
+      <c r="AO51">
+        <v>2.52</v>
+      </c>
+      <c r="AP51">
+        <v>1.55</v>
+      </c>
+      <c r="AQ51">
+        <v>2.74</v>
+      </c>
+      <c r="AR51">
+        <v>1.8</v>
+      </c>
+      <c r="AS51">
+        <v>708</v>
+      </c>
+      <c r="AT51">
+        <v>256</v>
+      </c>
+      <c r="AU51">
+        <v>345</v>
+      </c>
+      <c r="AV51">
+        <v>110</v>
+      </c>
+      <c r="AW51">
+        <v>281</v>
+      </c>
+      <c r="AX51">
+        <v>71</v>
+      </c>
+      <c r="AY51">
+        <v>28</v>
+      </c>
+      <c r="AZ51">
+        <v>16</v>
+      </c>
+      <c r="BA51">
+        <v>2</v>
+      </c>
+      <c r="BB51">
+        <v>3</v>
+      </c>
+      <c r="BC51">
+        <v>24</v>
+      </c>
+      <c r="BD51">
+        <v>20</v>
+      </c>
+      <c r="BE51">
+        <v>40</v>
+      </c>
+      <c r="BF51">
+        <v>18</v>
+      </c>
+      <c r="BG51">
+        <v>1</v>
+      </c>
+      <c r="BH51">
+        <v>5</v>
+      </c>
+      <c r="BI51" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ51" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK51">
+        <v>11</v>
+      </c>
+      <c r="BL51">
+        <v>12</v>
+      </c>
+      <c r="BM51">
+        <v>5</v>
+      </c>
+      <c r="BN51">
+        <v>14</v>
+      </c>
+      <c r="BO51">
+        <v>0</v>
+      </c>
+      <c r="BP51">
+        <v>6</v>
+      </c>
+      <c r="BQ51">
+        <v>21</v>
+      </c>
+      <c r="BR51">
+        <v>25</v>
+      </c>
+      <c r="BS51">
+        <v>2</v>
+      </c>
+      <c r="BT51">
+        <v>5</v>
+      </c>
+      <c r="BU51" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV51" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW51">
+        <v>48</v>
+      </c>
+      <c r="BX51">
+        <v>29</v>
+      </c>
+      <c r="BY51">
+        <v>33</v>
+      </c>
+      <c r="BZ51">
+        <v>20</v>
+      </c>
+      <c r="CA51">
+        <v>15</v>
+      </c>
+      <c r="CB51">
+        <v>9</v>
+      </c>
+      <c r="CC51">
+        <v>9</v>
+      </c>
+      <c r="CD51">
+        <v>6</v>
+      </c>
+      <c r="CE51" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF51" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG51">
+        <v>0</v>
+      </c>
+      <c r="CH51">
+        <v>5</v>
+      </c>
+      <c r="CI51">
+        <v>0</v>
+      </c>
+      <c r="CJ51">
         <v>0</v>
       </c>
     </row>

--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ligue 1 26-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3926C337-2C96-44EC-BE5B-2D1F9EAB0C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{181CC885-8B53-4490-A19B-673AA00475F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="143">
   <si>
     <t>date</t>
   </si>
@@ -460,6 +460,15 @@
   <si>
     <t>Sat 10 October, 20:45</t>
   </si>
+  <si>
+    <t>Sun 11 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 17:15</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -870,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ51"/>
+  <dimension ref="B1:CJ54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -1454,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H51" si="0">100-G3</f>
+        <f t="shared" ref="H3:H54" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -14367,6 +14376,798 @@
         <v>0</v>
       </c>
       <c r="CJ51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>46</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I52">
+        <v>1.25</v>
+      </c>
+      <c r="J52">
+        <v>0.63</v>
+      </c>
+      <c r="K52">
+        <v>11</v>
+      </c>
+      <c r="L52">
+        <v>11</v>
+      </c>
+      <c r="M52">
+        <v>6</v>
+      </c>
+      <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="O52">
+        <v>4</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>4</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>397</v>
+      </c>
+      <c r="T52">
+        <v>489</v>
+      </c>
+      <c r="U52">
+        <v>3</v>
+      </c>
+      <c r="V52">
+        <v>8</v>
+      </c>
+      <c r="W52">
+        <v>2</v>
+      </c>
+      <c r="X52">
+        <v>3</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA52">
+        <v>5</v>
+      </c>
+      <c r="AB52">
+        <v>5</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>3</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>10</v>
+      </c>
+      <c r="AH52">
+        <v>4</v>
+      </c>
+      <c r="AI52">
+        <v>1</v>
+      </c>
+      <c r="AJ52">
+        <v>7</v>
+      </c>
+      <c r="AK52">
+        <v>1.22</v>
+      </c>
+      <c r="AL52">
+        <v>0.36</v>
+      </c>
+      <c r="AM52">
+        <v>0.03</v>
+      </c>
+      <c r="AN52">
+        <v>0.27</v>
+      </c>
+      <c r="AO52">
+        <v>1.25</v>
+      </c>
+      <c r="AP52">
+        <v>0.63</v>
+      </c>
+      <c r="AQ52">
+        <v>1.25</v>
+      </c>
+      <c r="AR52">
+        <v>0.69</v>
+      </c>
+      <c r="AS52">
+        <v>454</v>
+      </c>
+      <c r="AT52">
+        <v>542</v>
+      </c>
+      <c r="AU52">
+        <v>264</v>
+      </c>
+      <c r="AV52">
+        <v>264</v>
+      </c>
+      <c r="AW52">
+        <v>133</v>
+      </c>
+      <c r="AX52">
+        <v>225</v>
+      </c>
+      <c r="AY52">
+        <v>24</v>
+      </c>
+      <c r="AZ52">
+        <v>18</v>
+      </c>
+      <c r="BA52">
+        <v>3</v>
+      </c>
+      <c r="BB52">
+        <v>4</v>
+      </c>
+      <c r="BC52">
+        <v>17</v>
+      </c>
+      <c r="BD52">
+        <v>15</v>
+      </c>
+      <c r="BE52">
+        <v>24</v>
+      </c>
+      <c r="BF52">
+        <v>19</v>
+      </c>
+      <c r="BG52">
+        <v>5</v>
+      </c>
+      <c r="BH52">
+        <v>2</v>
+      </c>
+      <c r="BI52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK52">
+        <v>23</v>
+      </c>
+      <c r="BL52">
+        <v>20</v>
+      </c>
+      <c r="BM52">
+        <v>8</v>
+      </c>
+      <c r="BN52">
+        <v>12</v>
+      </c>
+      <c r="BO52">
+        <v>3</v>
+      </c>
+      <c r="BP52">
+        <v>1</v>
+      </c>
+      <c r="BQ52">
+        <v>23</v>
+      </c>
+      <c r="BR52">
+        <v>15</v>
+      </c>
+      <c r="BS52">
+        <v>2</v>
+      </c>
+      <c r="BT52">
+        <v>4</v>
+      </c>
+      <c r="BU52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW52">
+        <v>42</v>
+      </c>
+      <c r="BX52">
+        <v>39</v>
+      </c>
+      <c r="BY52">
+        <v>37</v>
+      </c>
+      <c r="BZ52">
+        <v>33</v>
+      </c>
+      <c r="CA52">
+        <v>5</v>
+      </c>
+      <c r="CB52">
+        <v>6</v>
+      </c>
+      <c r="CC52">
+        <v>6</v>
+      </c>
+      <c r="CD52">
+        <v>10</v>
+      </c>
+      <c r="CE52" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF52" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG52">
+        <v>1</v>
+      </c>
+      <c r="CH52">
+        <v>1</v>
+      </c>
+      <c r="CI52">
+        <v>0</v>
+      </c>
+      <c r="CJ52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>59</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="I53">
+        <v>2.56</v>
+      </c>
+      <c r="J53">
+        <v>1.76</v>
+      </c>
+      <c r="K53">
+        <v>21</v>
+      </c>
+      <c r="L53">
+        <v>12</v>
+      </c>
+      <c r="M53">
+        <v>10</v>
+      </c>
+      <c r="N53">
+        <v>5</v>
+      </c>
+      <c r="O53">
+        <v>3</v>
+      </c>
+      <c r="P53">
+        <v>2</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <v>459</v>
+      </c>
+      <c r="T53">
+        <v>293</v>
+      </c>
+      <c r="U53">
+        <v>12</v>
+      </c>
+      <c r="V53">
+        <v>11</v>
+      </c>
+      <c r="W53">
+        <v>12</v>
+      </c>
+      <c r="X53">
+        <v>5</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA53">
+        <v>5</v>
+      </c>
+      <c r="AB53">
+        <v>4</v>
+      </c>
+      <c r="AC53">
+        <v>6</v>
+      </c>
+      <c r="AD53">
+        <v>3</v>
+      </c>
+      <c r="AE53">
+        <v>1</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>13</v>
+      </c>
+      <c r="AH53">
+        <v>5</v>
+      </c>
+      <c r="AI53">
+        <v>8</v>
+      </c>
+      <c r="AJ53">
+        <v>7</v>
+      </c>
+      <c r="AK53">
+        <v>1.87</v>
+      </c>
+      <c r="AL53">
+        <v>1.65</v>
+      </c>
+      <c r="AM53">
+        <v>0.7</v>
+      </c>
+      <c r="AN53">
+        <v>0.11</v>
+      </c>
+      <c r="AO53">
+        <v>2.56</v>
+      </c>
+      <c r="AP53">
+        <v>1.76</v>
+      </c>
+      <c r="AQ53">
+        <v>3.71</v>
+      </c>
+      <c r="AR53">
+        <v>1.73</v>
+      </c>
+      <c r="AS53">
+        <v>534</v>
+      </c>
+      <c r="AT53">
+        <v>377</v>
+      </c>
+      <c r="AU53">
+        <v>214</v>
+      </c>
+      <c r="AV53">
+        <v>160</v>
+      </c>
+      <c r="AW53">
+        <v>245</v>
+      </c>
+      <c r="AX53">
+        <v>133</v>
+      </c>
+      <c r="AY53">
+        <v>18</v>
+      </c>
+      <c r="AZ53">
+        <v>17</v>
+      </c>
+      <c r="BA53">
+        <v>7</v>
+      </c>
+      <c r="BB53">
+        <v>2</v>
+      </c>
+      <c r="BC53">
+        <v>26</v>
+      </c>
+      <c r="BD53">
+        <v>19</v>
+      </c>
+      <c r="BE53">
+        <v>25</v>
+      </c>
+      <c r="BF53">
+        <v>16</v>
+      </c>
+      <c r="BG53">
+        <v>2</v>
+      </c>
+      <c r="BH53">
+        <v>4</v>
+      </c>
+      <c r="BI53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK53">
+        <v>18</v>
+      </c>
+      <c r="BL53">
+        <v>20</v>
+      </c>
+      <c r="BM53">
+        <v>8</v>
+      </c>
+      <c r="BN53">
+        <v>7</v>
+      </c>
+      <c r="BO53">
+        <v>3</v>
+      </c>
+      <c r="BP53">
+        <v>6</v>
+      </c>
+      <c r="BQ53">
+        <v>17</v>
+      </c>
+      <c r="BR53">
+        <v>25</v>
+      </c>
+      <c r="BS53">
+        <v>4</v>
+      </c>
+      <c r="BT53">
+        <v>6</v>
+      </c>
+      <c r="BU53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW53">
+        <v>45</v>
+      </c>
+      <c r="BX53">
+        <v>53</v>
+      </c>
+      <c r="BY53">
+        <v>32</v>
+      </c>
+      <c r="BZ53">
+        <v>42</v>
+      </c>
+      <c r="CA53">
+        <v>13</v>
+      </c>
+      <c r="CB53">
+        <v>11</v>
+      </c>
+      <c r="CC53">
+        <v>4</v>
+      </c>
+      <c r="CD53">
+        <v>11</v>
+      </c>
+      <c r="CE53" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF53" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG53">
+        <v>4</v>
+      </c>
+      <c r="CH53">
+        <v>0</v>
+      </c>
+      <c r="CI53">
+        <v>0</v>
+      </c>
+      <c r="CJ53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>36</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="I54">
+        <v>1.06</v>
+      </c>
+      <c r="J54">
+        <v>1.3</v>
+      </c>
+      <c r="K54">
+        <v>15</v>
+      </c>
+      <c r="L54">
+        <v>5</v>
+      </c>
+      <c r="M54">
+        <v>3</v>
+      </c>
+      <c r="N54">
+        <v>2</v>
+      </c>
+      <c r="O54">
+        <v>2</v>
+      </c>
+      <c r="P54">
+        <v>2</v>
+      </c>
+      <c r="Q54">
+        <v>2</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>281</v>
+      </c>
+      <c r="T54">
+        <v>573</v>
+      </c>
+      <c r="U54">
+        <v>14</v>
+      </c>
+      <c r="V54">
+        <v>15</v>
+      </c>
+      <c r="W54">
+        <v>6</v>
+      </c>
+      <c r="X54">
+        <v>3</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA54">
+        <v>8</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>4</v>
+      </c>
+      <c r="AD54">
+        <v>3</v>
+      </c>
+      <c r="AE54">
+        <v>2</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>13</v>
+      </c>
+      <c r="AH54">
+        <v>5</v>
+      </c>
+      <c r="AI54">
+        <v>2</v>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0.88</v>
+      </c>
+      <c r="AL54">
+        <v>0.27</v>
+      </c>
+      <c r="AM54">
+        <v>0.18</v>
+      </c>
+      <c r="AN54">
+        <v>0.24</v>
+      </c>
+      <c r="AO54">
+        <v>1.06</v>
+      </c>
+      <c r="AP54">
+        <v>0.51</v>
+      </c>
+      <c r="AQ54">
+        <v>0.16</v>
+      </c>
+      <c r="AR54">
+        <v>1.01</v>
+      </c>
+      <c r="AS54">
+        <v>350</v>
+      </c>
+      <c r="AT54">
+        <v>644</v>
+      </c>
+      <c r="AU54">
+        <v>161</v>
+      </c>
+      <c r="AV54">
+        <v>356</v>
+      </c>
+      <c r="AW54">
+        <v>120</v>
+      </c>
+      <c r="AX54">
+        <v>217</v>
+      </c>
+      <c r="AY54">
+        <v>15</v>
+      </c>
+      <c r="AZ54">
+        <v>13</v>
+      </c>
+      <c r="BA54">
+        <v>11</v>
+      </c>
+      <c r="BB54">
+        <v>2</v>
+      </c>
+      <c r="BC54">
+        <v>15</v>
+      </c>
+      <c r="BD54">
+        <v>16</v>
+      </c>
+      <c r="BE54">
+        <v>21</v>
+      </c>
+      <c r="BF54">
+        <v>20</v>
+      </c>
+      <c r="BG54">
+        <v>2</v>
+      </c>
+      <c r="BH54">
+        <v>2</v>
+      </c>
+      <c r="BI54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK54">
+        <v>17</v>
+      </c>
+      <c r="BL54">
+        <v>14</v>
+      </c>
+      <c r="BM54">
+        <v>9</v>
+      </c>
+      <c r="BN54">
+        <v>8</v>
+      </c>
+      <c r="BO54">
+        <v>3</v>
+      </c>
+      <c r="BP54">
+        <v>4</v>
+      </c>
+      <c r="BQ54">
+        <v>15</v>
+      </c>
+      <c r="BR54">
+        <v>30</v>
+      </c>
+      <c r="BS54">
+        <v>0</v>
+      </c>
+      <c r="BT54">
+        <v>3</v>
+      </c>
+      <c r="BU54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW54">
+        <v>55</v>
+      </c>
+      <c r="BX54">
+        <v>44</v>
+      </c>
+      <c r="BY54">
+        <v>34</v>
+      </c>
+      <c r="BZ54">
+        <v>32</v>
+      </c>
+      <c r="CA54">
+        <v>21</v>
+      </c>
+      <c r="CB54">
+        <v>12</v>
+      </c>
+      <c r="CC54">
+        <v>5</v>
+      </c>
+      <c r="CD54">
+        <v>6</v>
+      </c>
+      <c r="CE54" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF54" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG54">
+        <v>4</v>
+      </c>
+      <c r="CH54">
+        <v>1</v>
+      </c>
+      <c r="CI54">
+        <v>0</v>
+      </c>
+      <c r="CJ54">
         <v>0</v>
       </c>
     </row>

--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{181CC885-8B53-4490-A19B-673AA00475F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{795AE4BB-AB69-4AAD-A222-68F28B1B0543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="144">
   <si>
     <t>date</t>
   </si>
@@ -469,6 +469,9 @@
   <si>
     <t>Sun 11 October, 20:45</t>
   </si>
+  <si>
+    <t>Fri 16 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -879,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ54"/>
+  <dimension ref="B1:CJ55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -1463,7 +1466,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H54" si="0">100-G3</f>
+        <f t="shared" ref="H3:H55" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -15168,6 +15171,270 @@
         <v>0</v>
       </c>
       <c r="CJ54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>53</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I55">
+        <v>0.95</v>
+      </c>
+      <c r="J55">
+        <v>1.81</v>
+      </c>
+      <c r="K55">
+        <v>11</v>
+      </c>
+      <c r="L55">
+        <v>13</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>5</v>
+      </c>
+      <c r="O55">
+        <v>2</v>
+      </c>
+      <c r="P55">
+        <v>2</v>
+      </c>
+      <c r="Q55">
+        <v>2</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>489</v>
+      </c>
+      <c r="T55">
+        <v>450</v>
+      </c>
+      <c r="U55">
+        <v>15</v>
+      </c>
+      <c r="V55">
+        <v>9</v>
+      </c>
+      <c r="W55">
+        <v>2</v>
+      </c>
+      <c r="X55">
+        <v>2</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA55">
+        <v>6</v>
+      </c>
+      <c r="AB55">
+        <v>7</v>
+      </c>
+      <c r="AC55">
+        <v>4</v>
+      </c>
+      <c r="AD55">
+        <v>1</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>7</v>
+      </c>
+      <c r="AH55">
+        <v>9</v>
+      </c>
+      <c r="AI55">
+        <v>4</v>
+      </c>
+      <c r="AJ55">
+        <v>4</v>
+      </c>
+      <c r="AK55">
+        <v>0.67</v>
+      </c>
+      <c r="AL55">
+        <v>1.61</v>
+      </c>
+      <c r="AM55">
+        <v>0.27</v>
+      </c>
+      <c r="AN55">
+        <v>0.2</v>
+      </c>
+      <c r="AO55">
+        <v>0.95</v>
+      </c>
+      <c r="AP55">
+        <v>1.81</v>
+      </c>
+      <c r="AQ55">
+        <v>0.16</v>
+      </c>
+      <c r="AR55">
+        <v>3.91</v>
+      </c>
+      <c r="AS55">
+        <v>564</v>
+      </c>
+      <c r="AT55">
+        <v>526</v>
+      </c>
+      <c r="AU55">
+        <v>249</v>
+      </c>
+      <c r="AV55">
+        <v>277</v>
+      </c>
+      <c r="AW55">
+        <v>240</v>
+      </c>
+      <c r="AX55">
+        <v>173</v>
+      </c>
+      <c r="AY55">
+        <v>27</v>
+      </c>
+      <c r="AZ55">
+        <v>23</v>
+      </c>
+      <c r="BA55">
+        <v>7</v>
+      </c>
+      <c r="BB55">
+        <v>1</v>
+      </c>
+      <c r="BC55">
+        <v>17</v>
+      </c>
+      <c r="BD55">
+        <v>14</v>
+      </c>
+      <c r="BE55">
+        <v>20</v>
+      </c>
+      <c r="BF55">
+        <v>17</v>
+      </c>
+      <c r="BG55">
+        <v>0</v>
+      </c>
+      <c r="BH55">
+        <v>3</v>
+      </c>
+      <c r="BI55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK55">
+        <v>11</v>
+      </c>
+      <c r="BL55">
+        <v>13</v>
+      </c>
+      <c r="BM55">
+        <v>4</v>
+      </c>
+      <c r="BN55">
+        <v>7</v>
+      </c>
+      <c r="BO55">
+        <v>1</v>
+      </c>
+      <c r="BP55">
+        <v>4</v>
+      </c>
+      <c r="BQ55">
+        <v>16</v>
+      </c>
+      <c r="BR55">
+        <v>32</v>
+      </c>
+      <c r="BS55">
+        <v>2</v>
+      </c>
+      <c r="BT55">
+        <v>1</v>
+      </c>
+      <c r="BU55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW55">
+        <v>36</v>
+      </c>
+      <c r="BX55">
+        <v>54</v>
+      </c>
+      <c r="BY55">
+        <v>26</v>
+      </c>
+      <c r="BZ55">
+        <v>32</v>
+      </c>
+      <c r="CA55">
+        <v>10</v>
+      </c>
+      <c r="CB55">
+        <v>22</v>
+      </c>
+      <c r="CC55">
+        <v>6</v>
+      </c>
+      <c r="CD55">
+        <v>6</v>
+      </c>
+      <c r="CE55" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF55" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG55">
+        <v>2</v>
+      </c>
+      <c r="CH55">
+        <v>1</v>
+      </c>
+      <c r="CI55">
+        <v>0</v>
+      </c>
+      <c r="CJ55">
         <v>0</v>
       </c>
     </row>

--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{795AE4BB-AB69-4AAD-A222-68F28B1B0543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E559E14D-908A-4677-993C-838F930B17DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="148">
   <si>
     <t>date</t>
   </si>
@@ -472,6 +472,18 @@
   <si>
     <t>Fri 16 October, 20:45</t>
   </si>
+  <si>
+    <t>Sat 17 October, 17:15</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 20:45</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 17:15</t>
+  </si>
 </sst>
 </file>
 
@@ -882,10 +894,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ55"/>
+  <dimension ref="B1:CJ62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
@@ -1466,7 +1478,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H55" si="0">100-G3</f>
+        <f t="shared" ref="H3:H62" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -15435,6 +15447,1854 @@
         <v>0</v>
       </c>
       <c r="CJ55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>27</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="I56">
+        <v>1.47</v>
+      </c>
+      <c r="J56">
+        <v>2.69</v>
+      </c>
+      <c r="K56">
+        <v>17</v>
+      </c>
+      <c r="L56">
+        <v>18</v>
+      </c>
+      <c r="M56">
+        <v>8</v>
+      </c>
+      <c r="N56">
+        <v>7</v>
+      </c>
+      <c r="O56">
+        <v>4</v>
+      </c>
+      <c r="P56">
+        <v>7</v>
+      </c>
+      <c r="Q56">
+        <v>4</v>
+      </c>
+      <c r="R56">
+        <v>5</v>
+      </c>
+      <c r="S56">
+        <v>194</v>
+      </c>
+      <c r="T56">
+        <v>617</v>
+      </c>
+      <c r="U56">
+        <v>12</v>
+      </c>
+      <c r="V56">
+        <v>6</v>
+      </c>
+      <c r="W56">
+        <v>3</v>
+      </c>
+      <c r="X56">
+        <v>6</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA56">
+        <v>7</v>
+      </c>
+      <c r="AB56">
+        <v>5</v>
+      </c>
+      <c r="AC56">
+        <v>2</v>
+      </c>
+      <c r="AD56">
+        <v>6</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>14</v>
+      </c>
+      <c r="AH56">
+        <v>14</v>
+      </c>
+      <c r="AI56">
+        <v>3</v>
+      </c>
+      <c r="AJ56">
+        <v>4</v>
+      </c>
+      <c r="AK56">
+        <v>0.65</v>
+      </c>
+      <c r="AL56">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AM56">
+        <v>0.82</v>
+      </c>
+      <c r="AN56">
+        <v>0.81</v>
+      </c>
+      <c r="AO56">
+        <v>1.47</v>
+      </c>
+      <c r="AP56">
+        <v>1.9</v>
+      </c>
+      <c r="AQ56">
+        <v>2.21</v>
+      </c>
+      <c r="AR56">
+        <v>2.66</v>
+      </c>
+      <c r="AS56">
+        <v>246</v>
+      </c>
+      <c r="AT56">
+        <v>672</v>
+      </c>
+      <c r="AU56">
+        <v>101</v>
+      </c>
+      <c r="AV56">
+        <v>245</v>
+      </c>
+      <c r="AW56">
+        <v>93</v>
+      </c>
+      <c r="AX56">
+        <v>372</v>
+      </c>
+      <c r="AY56">
+        <v>16</v>
+      </c>
+      <c r="AZ56">
+        <v>36</v>
+      </c>
+      <c r="BA56">
+        <v>4</v>
+      </c>
+      <c r="BB56">
+        <v>4</v>
+      </c>
+      <c r="BC56">
+        <v>22</v>
+      </c>
+      <c r="BD56">
+        <v>16</v>
+      </c>
+      <c r="BE56">
+        <v>22</v>
+      </c>
+      <c r="BF56">
+        <v>43</v>
+      </c>
+      <c r="BG56">
+        <v>2</v>
+      </c>
+      <c r="BH56">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK56">
+        <v>20</v>
+      </c>
+      <c r="BL56">
+        <v>13</v>
+      </c>
+      <c r="BM56">
+        <v>11</v>
+      </c>
+      <c r="BN56">
+        <v>4</v>
+      </c>
+      <c r="BO56">
+        <v>5</v>
+      </c>
+      <c r="BP56">
+        <v>2</v>
+      </c>
+      <c r="BQ56">
+        <v>21</v>
+      </c>
+      <c r="BR56">
+        <v>7</v>
+      </c>
+      <c r="BS56">
+        <v>4</v>
+      </c>
+      <c r="BT56">
+        <v>7</v>
+      </c>
+      <c r="BU56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW56">
+        <v>40</v>
+      </c>
+      <c r="BX56">
+        <v>42</v>
+      </c>
+      <c r="BY56">
+        <v>30</v>
+      </c>
+      <c r="BZ56">
+        <v>33</v>
+      </c>
+      <c r="CA56">
+        <v>10</v>
+      </c>
+      <c r="CB56">
+        <v>9</v>
+      </c>
+      <c r="CC56">
+        <v>4</v>
+      </c>
+      <c r="CD56">
+        <v>9</v>
+      </c>
+      <c r="CE56" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF56" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG56">
+        <v>2</v>
+      </c>
+      <c r="CH56">
+        <v>0</v>
+      </c>
+      <c r="CI56">
+        <v>0</v>
+      </c>
+      <c r="CJ56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>67</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="I57">
+        <v>2.17</v>
+      </c>
+      <c r="J57">
+        <v>0.78</v>
+      </c>
+      <c r="K57">
+        <v>17</v>
+      </c>
+      <c r="L57">
+        <v>8</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57">
+        <v>3</v>
+      </c>
+      <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>584</v>
+      </c>
+      <c r="T57">
+        <v>348</v>
+      </c>
+      <c r="U57">
+        <v>12</v>
+      </c>
+      <c r="V57">
+        <v>20</v>
+      </c>
+      <c r="W57">
+        <v>5</v>
+      </c>
+      <c r="X57">
+        <v>2</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA57">
+        <v>9</v>
+      </c>
+      <c r="AB57">
+        <v>3</v>
+      </c>
+      <c r="AC57">
+        <v>3</v>
+      </c>
+      <c r="AD57">
+        <v>3</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>10</v>
+      </c>
+      <c r="AH57">
+        <v>6</v>
+      </c>
+      <c r="AI57">
+        <v>7</v>
+      </c>
+      <c r="AJ57">
+        <v>2</v>
+      </c>
+      <c r="AK57">
+        <v>0.47</v>
+      </c>
+      <c r="AL57">
+        <v>0.53</v>
+      </c>
+      <c r="AM57">
+        <v>0.92</v>
+      </c>
+      <c r="AN57">
+        <v>0.25</v>
+      </c>
+      <c r="AO57">
+        <v>1.38</v>
+      </c>
+      <c r="AP57">
+        <v>0.78</v>
+      </c>
+      <c r="AQ57">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AR57">
+        <v>0.87</v>
+      </c>
+      <c r="AS57">
+        <v>645</v>
+      </c>
+      <c r="AT57">
+        <v>320</v>
+      </c>
+      <c r="AU57">
+        <v>286</v>
+      </c>
+      <c r="AV57">
+        <v>180</v>
+      </c>
+      <c r="AW57">
+        <v>298</v>
+      </c>
+      <c r="AX57">
+        <v>68</v>
+      </c>
+      <c r="AY57">
+        <v>21</v>
+      </c>
+      <c r="AZ57">
+        <v>26</v>
+      </c>
+      <c r="BA57">
+        <v>7</v>
+      </c>
+      <c r="BB57">
+        <v>2</v>
+      </c>
+      <c r="BC57">
+        <v>24</v>
+      </c>
+      <c r="BD57">
+        <v>16</v>
+      </c>
+      <c r="BE57">
+        <v>44</v>
+      </c>
+      <c r="BF57">
+        <v>12</v>
+      </c>
+      <c r="BG57">
+        <v>3</v>
+      </c>
+      <c r="BH57">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK57">
+        <v>23</v>
+      </c>
+      <c r="BL57">
+        <v>19</v>
+      </c>
+      <c r="BM57">
+        <v>9</v>
+      </c>
+      <c r="BN57">
+        <v>7</v>
+      </c>
+      <c r="BO57">
+        <v>2</v>
+      </c>
+      <c r="BP57">
+        <v>3</v>
+      </c>
+      <c r="BQ57">
+        <v>8</v>
+      </c>
+      <c r="BR57">
+        <v>39</v>
+      </c>
+      <c r="BS57">
+        <v>1</v>
+      </c>
+      <c r="BT57">
+        <v>4</v>
+      </c>
+      <c r="BU57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW57">
+        <v>63</v>
+      </c>
+      <c r="BX57">
+        <v>44</v>
+      </c>
+      <c r="BY57">
+        <v>54</v>
+      </c>
+      <c r="BZ57">
+        <v>37</v>
+      </c>
+      <c r="CA57">
+        <v>9</v>
+      </c>
+      <c r="CB57">
+        <v>7</v>
+      </c>
+      <c r="CC57">
+        <v>13</v>
+      </c>
+      <c r="CD57">
+        <v>6</v>
+      </c>
+      <c r="CE57" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF57" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG57">
+        <v>1</v>
+      </c>
+      <c r="CH57">
+        <v>2</v>
+      </c>
+      <c r="CI57">
+        <v>0</v>
+      </c>
+      <c r="CJ57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>41</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="I58">
+        <v>1.24</v>
+      </c>
+      <c r="J58">
+        <v>1.43</v>
+      </c>
+      <c r="K58">
+        <v>12</v>
+      </c>
+      <c r="L58">
+        <v>13</v>
+      </c>
+      <c r="M58">
+        <v>5</v>
+      </c>
+      <c r="N58">
+        <v>3</v>
+      </c>
+      <c r="O58">
+        <v>3</v>
+      </c>
+      <c r="P58">
+        <v>2</v>
+      </c>
+      <c r="Q58">
+        <v>2</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>306</v>
+      </c>
+      <c r="T58">
+        <v>451</v>
+      </c>
+      <c r="U58">
+        <v>13</v>
+      </c>
+      <c r="V58">
+        <v>11</v>
+      </c>
+      <c r="W58">
+        <v>6</v>
+      </c>
+      <c r="X58">
+        <v>4</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA58">
+        <v>4</v>
+      </c>
+      <c r="AB58">
+        <v>6</v>
+      </c>
+      <c r="AC58">
+        <v>3</v>
+      </c>
+      <c r="AD58">
+        <v>4</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>1</v>
+      </c>
+      <c r="AG58">
+        <v>7</v>
+      </c>
+      <c r="AH58">
+        <v>9</v>
+      </c>
+      <c r="AI58">
+        <v>5</v>
+      </c>
+      <c r="AJ58">
+        <v>4</v>
+      </c>
+      <c r="AK58">
+        <v>1.08</v>
+      </c>
+      <c r="AL58">
+        <v>1.27</v>
+      </c>
+      <c r="AM58">
+        <v>0.16</v>
+      </c>
+      <c r="AN58">
+        <v>0.16</v>
+      </c>
+      <c r="AO58">
+        <v>1.24</v>
+      </c>
+      <c r="AP58">
+        <v>1.43</v>
+      </c>
+      <c r="AQ58">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AR58">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AS58">
+        <v>372</v>
+      </c>
+      <c r="AT58">
+        <v>540</v>
+      </c>
+      <c r="AU58">
+        <v>135</v>
+      </c>
+      <c r="AV58">
+        <v>306</v>
+      </c>
+      <c r="AW58">
+        <v>171</v>
+      </c>
+      <c r="AX58">
+        <v>145</v>
+      </c>
+      <c r="AY58">
+        <v>34</v>
+      </c>
+      <c r="AZ58">
+        <v>24</v>
+      </c>
+      <c r="BA58">
+        <v>5</v>
+      </c>
+      <c r="BB58">
+        <v>8</v>
+      </c>
+      <c r="BC58">
+        <v>16</v>
+      </c>
+      <c r="BD58">
+        <v>14</v>
+      </c>
+      <c r="BE58">
+        <v>31</v>
+      </c>
+      <c r="BF58">
+        <v>20</v>
+      </c>
+      <c r="BG58">
+        <v>0</v>
+      </c>
+      <c r="BH58">
+        <v>1</v>
+      </c>
+      <c r="BI58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK58">
+        <v>13</v>
+      </c>
+      <c r="BL58">
+        <v>16</v>
+      </c>
+      <c r="BM58">
+        <v>13</v>
+      </c>
+      <c r="BN58">
+        <v>8</v>
+      </c>
+      <c r="BO58">
+        <v>4</v>
+      </c>
+      <c r="BP58">
+        <v>3</v>
+      </c>
+      <c r="BQ58">
+        <v>24</v>
+      </c>
+      <c r="BR58">
+        <v>14</v>
+      </c>
+      <c r="BS58">
+        <v>1</v>
+      </c>
+      <c r="BT58">
+        <v>4</v>
+      </c>
+      <c r="BU58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW58">
+        <v>36</v>
+      </c>
+      <c r="BX58">
+        <v>40</v>
+      </c>
+      <c r="BY58">
+        <v>29</v>
+      </c>
+      <c r="BZ58">
+        <v>33</v>
+      </c>
+      <c r="CA58">
+        <v>7</v>
+      </c>
+      <c r="CB58">
+        <v>7</v>
+      </c>
+      <c r="CC58">
+        <v>5</v>
+      </c>
+      <c r="CD58">
+        <v>5</v>
+      </c>
+      <c r="CE58" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF58" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG58">
+        <v>2</v>
+      </c>
+      <c r="CH58">
+        <v>2</v>
+      </c>
+      <c r="CI58">
+        <v>0</v>
+      </c>
+      <c r="CJ58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B59" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>42</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I59">
+        <v>2.02</v>
+      </c>
+      <c r="J59">
+        <v>2.74</v>
+      </c>
+      <c r="K59">
+        <v>11</v>
+      </c>
+      <c r="L59">
+        <v>21</v>
+      </c>
+      <c r="M59">
+        <v>3</v>
+      </c>
+      <c r="N59">
+        <v>8</v>
+      </c>
+      <c r="O59">
+        <v>2</v>
+      </c>
+      <c r="P59">
+        <v>5</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <v>328</v>
+      </c>
+      <c r="T59">
+        <v>494</v>
+      </c>
+      <c r="U59">
+        <v>11</v>
+      </c>
+      <c r="V59">
+        <v>12</v>
+      </c>
+      <c r="W59">
+        <v>2</v>
+      </c>
+      <c r="X59">
+        <v>5</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA59">
+        <v>4</v>
+      </c>
+      <c r="AB59">
+        <v>8</v>
+      </c>
+      <c r="AC59">
+        <v>4</v>
+      </c>
+      <c r="AD59">
+        <v>5</v>
+      </c>
+      <c r="AE59">
+        <v>1</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>7</v>
+      </c>
+      <c r="AH59">
+        <v>13</v>
+      </c>
+      <c r="AI59">
+        <v>4</v>
+      </c>
+      <c r="AJ59">
+        <v>8</v>
+      </c>
+      <c r="AK59">
+        <v>1.2</v>
+      </c>
+      <c r="AL59">
+        <v>1.65</v>
+      </c>
+      <c r="AM59">
+        <v>0.03</v>
+      </c>
+      <c r="AN59">
+        <v>0.31</v>
+      </c>
+      <c r="AO59">
+        <v>1.23</v>
+      </c>
+      <c r="AP59">
+        <v>1.95</v>
+      </c>
+      <c r="AQ59">
+        <v>1.96</v>
+      </c>
+      <c r="AR59">
+        <v>4.51</v>
+      </c>
+      <c r="AS59">
+        <v>390</v>
+      </c>
+      <c r="AT59">
+        <v>564</v>
+      </c>
+      <c r="AU59">
+        <v>202</v>
+      </c>
+      <c r="AV59">
+        <v>221</v>
+      </c>
+      <c r="AW59">
+        <v>126</v>
+      </c>
+      <c r="AX59">
+        <v>273</v>
+      </c>
+      <c r="AY59">
+        <v>35</v>
+      </c>
+      <c r="AZ59">
+        <v>21</v>
+      </c>
+      <c r="BA59">
+        <v>4</v>
+      </c>
+      <c r="BB59">
+        <v>4</v>
+      </c>
+      <c r="BC59">
+        <v>19</v>
+      </c>
+      <c r="BD59">
+        <v>22</v>
+      </c>
+      <c r="BE59">
+        <v>18</v>
+      </c>
+      <c r="BF59">
+        <v>33</v>
+      </c>
+      <c r="BG59">
+        <v>0</v>
+      </c>
+      <c r="BH59">
+        <v>0</v>
+      </c>
+      <c r="BI59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK59">
+        <v>14</v>
+      </c>
+      <c r="BL59">
+        <v>8</v>
+      </c>
+      <c r="BM59">
+        <v>10</v>
+      </c>
+      <c r="BN59">
+        <v>12</v>
+      </c>
+      <c r="BO59">
+        <v>5</v>
+      </c>
+      <c r="BP59">
+        <v>4</v>
+      </c>
+      <c r="BQ59">
+        <v>33</v>
+      </c>
+      <c r="BR59">
+        <v>21</v>
+      </c>
+      <c r="BS59">
+        <v>3</v>
+      </c>
+      <c r="BT59">
+        <v>1</v>
+      </c>
+      <c r="BU59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW59">
+        <v>40</v>
+      </c>
+      <c r="BX59">
+        <v>31</v>
+      </c>
+      <c r="BY59">
+        <v>31</v>
+      </c>
+      <c r="BZ59">
+        <v>22</v>
+      </c>
+      <c r="CA59">
+        <v>9</v>
+      </c>
+      <c r="CB59">
+        <v>9</v>
+      </c>
+      <c r="CC59">
+        <v>6</v>
+      </c>
+      <c r="CD59">
+        <v>4</v>
+      </c>
+      <c r="CE59" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF59" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG59">
+        <v>1</v>
+      </c>
+      <c r="CH59">
+        <v>1</v>
+      </c>
+      <c r="CI59">
+        <v>0</v>
+      </c>
+      <c r="CJ59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B60" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>52</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="I60">
+        <v>1.41</v>
+      </c>
+      <c r="J60">
+        <v>2.73</v>
+      </c>
+      <c r="K60">
+        <v>15</v>
+      </c>
+      <c r="L60">
+        <v>13</v>
+      </c>
+      <c r="M60">
+        <v>6</v>
+      </c>
+      <c r="N60">
+        <v>6</v>
+      </c>
+      <c r="O60">
+        <v>3</v>
+      </c>
+      <c r="P60">
+        <v>2</v>
+      </c>
+      <c r="Q60">
+        <v>2</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>339</v>
+      </c>
+      <c r="T60">
+        <v>350</v>
+      </c>
+      <c r="U60">
+        <v>16</v>
+      </c>
+      <c r="V60">
+        <v>22</v>
+      </c>
+      <c r="W60">
+        <v>7</v>
+      </c>
+      <c r="X60">
+        <v>4</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA60">
+        <v>5</v>
+      </c>
+      <c r="AB60">
+        <v>5</v>
+      </c>
+      <c r="AC60">
+        <v>4</v>
+      </c>
+      <c r="AD60">
+        <v>2</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>1</v>
+      </c>
+      <c r="AG60">
+        <v>13</v>
+      </c>
+      <c r="AH60">
+        <v>11</v>
+      </c>
+      <c r="AI60">
+        <v>2</v>
+      </c>
+      <c r="AJ60">
+        <v>2</v>
+      </c>
+      <c r="AK60">
+        <v>1.01</v>
+      </c>
+      <c r="AL60">
+        <v>2.04</v>
+      </c>
+      <c r="AM60">
+        <v>0.4</v>
+      </c>
+      <c r="AN60">
+        <v>0.69</v>
+      </c>
+      <c r="AO60">
+        <v>1.41</v>
+      </c>
+      <c r="AP60">
+        <v>2.73</v>
+      </c>
+      <c r="AQ60">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AR60">
+        <v>3.15</v>
+      </c>
+      <c r="AS60">
+        <v>417</v>
+      </c>
+      <c r="AT60">
+        <v>409</v>
+      </c>
+      <c r="AU60">
+        <v>192</v>
+      </c>
+      <c r="AV60">
+        <v>197</v>
+      </c>
+      <c r="AW60">
+        <v>147</v>
+      </c>
+      <c r="AX60">
+        <v>153</v>
+      </c>
+      <c r="AY60">
+        <v>22</v>
+      </c>
+      <c r="AZ60">
+        <v>22</v>
+      </c>
+      <c r="BA60">
+        <v>5</v>
+      </c>
+      <c r="BB60">
+        <v>2</v>
+      </c>
+      <c r="BC60">
+        <v>27</v>
+      </c>
+      <c r="BD60">
+        <v>17</v>
+      </c>
+      <c r="BE60">
+        <v>28</v>
+      </c>
+      <c r="BF60">
+        <v>18</v>
+      </c>
+      <c r="BG60">
+        <v>2</v>
+      </c>
+      <c r="BH60">
+        <v>2</v>
+      </c>
+      <c r="BI60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK60">
+        <v>29</v>
+      </c>
+      <c r="BL60">
+        <v>16</v>
+      </c>
+      <c r="BM60">
+        <v>12</v>
+      </c>
+      <c r="BN60">
+        <v>10</v>
+      </c>
+      <c r="BO60">
+        <v>2</v>
+      </c>
+      <c r="BP60">
+        <v>4</v>
+      </c>
+      <c r="BQ60">
+        <v>19</v>
+      </c>
+      <c r="BR60">
+        <v>41</v>
+      </c>
+      <c r="BS60">
+        <v>3</v>
+      </c>
+      <c r="BT60">
+        <v>6</v>
+      </c>
+      <c r="BU60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW60">
+        <v>65</v>
+      </c>
+      <c r="BX60">
+        <v>59</v>
+      </c>
+      <c r="BY60">
+        <v>56</v>
+      </c>
+      <c r="BZ60">
+        <v>42</v>
+      </c>
+      <c r="CA60">
+        <v>9</v>
+      </c>
+      <c r="CB60">
+        <v>17</v>
+      </c>
+      <c r="CC60">
+        <v>5</v>
+      </c>
+      <c r="CD60">
+        <v>10</v>
+      </c>
+      <c r="CE60" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF60" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG60">
+        <v>1</v>
+      </c>
+      <c r="CH60">
+        <v>2</v>
+      </c>
+      <c r="CI60">
+        <v>0</v>
+      </c>
+      <c r="CJ60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B61" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>42</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I61">
+        <v>1.63</v>
+      </c>
+      <c r="J61">
+        <v>0.69</v>
+      </c>
+      <c r="K61">
+        <v>9</v>
+      </c>
+      <c r="L61">
+        <v>15</v>
+      </c>
+      <c r="M61">
+        <v>3</v>
+      </c>
+      <c r="N61">
+        <v>4</v>
+      </c>
+      <c r="O61">
+        <v>3</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>2</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>399</v>
+      </c>
+      <c r="T61">
+        <v>597</v>
+      </c>
+      <c r="U61">
+        <v>10</v>
+      </c>
+      <c r="V61">
+        <v>16</v>
+      </c>
+      <c r="W61">
+        <v>3</v>
+      </c>
+      <c r="X61">
+        <v>4</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA61">
+        <v>3</v>
+      </c>
+      <c r="AB61">
+        <v>6</v>
+      </c>
+      <c r="AC61">
+        <v>3</v>
+      </c>
+      <c r="AD61">
+        <v>5</v>
+      </c>
+      <c r="AE61">
+        <v>1</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>7</v>
+      </c>
+      <c r="AH61">
+        <v>9</v>
+      </c>
+      <c r="AI61">
+        <v>2</v>
+      </c>
+      <c r="AJ61">
+        <v>6</v>
+      </c>
+      <c r="AK61">
+        <v>0.77</v>
+      </c>
+      <c r="AL61">
+        <v>0.67</v>
+      </c>
+      <c r="AM61">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN61">
+        <v>0.02</v>
+      </c>
+      <c r="AO61">
+        <v>0.84</v>
+      </c>
+      <c r="AP61">
+        <v>0.69</v>
+      </c>
+      <c r="AQ61">
+        <v>1.58</v>
+      </c>
+      <c r="AR61">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS61">
+        <v>478</v>
+      </c>
+      <c r="AT61">
+        <v>661</v>
+      </c>
+      <c r="AU61">
+        <v>247</v>
+      </c>
+      <c r="AV61">
+        <v>222</v>
+      </c>
+      <c r="AW61">
+        <v>152</v>
+      </c>
+      <c r="AX61">
+        <v>375</v>
+      </c>
+      <c r="AY61">
+        <v>24</v>
+      </c>
+      <c r="AZ61">
+        <v>13</v>
+      </c>
+      <c r="BA61">
+        <v>5</v>
+      </c>
+      <c r="BB61">
+        <v>4</v>
+      </c>
+      <c r="BC61">
+        <v>19</v>
+      </c>
+      <c r="BD61">
+        <v>19</v>
+      </c>
+      <c r="BE61">
+        <v>26</v>
+      </c>
+      <c r="BF61">
+        <v>17</v>
+      </c>
+      <c r="BG61">
+        <v>1</v>
+      </c>
+      <c r="BH61">
+        <v>0</v>
+      </c>
+      <c r="BI61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK61">
+        <v>14</v>
+      </c>
+      <c r="BL61">
+        <v>16</v>
+      </c>
+      <c r="BM61">
+        <v>15</v>
+      </c>
+      <c r="BN61">
+        <v>16</v>
+      </c>
+      <c r="BO61">
+        <v>4</v>
+      </c>
+      <c r="BP61">
+        <v>3</v>
+      </c>
+      <c r="BQ61">
+        <v>23</v>
+      </c>
+      <c r="BR61">
+        <v>20</v>
+      </c>
+      <c r="BS61">
+        <v>4</v>
+      </c>
+      <c r="BT61">
+        <v>2</v>
+      </c>
+      <c r="BU61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW61">
+        <v>47</v>
+      </c>
+      <c r="BX61">
+        <v>38</v>
+      </c>
+      <c r="BY61">
+        <v>38</v>
+      </c>
+      <c r="BZ61">
+        <v>29</v>
+      </c>
+      <c r="CA61">
+        <v>9</v>
+      </c>
+      <c r="CB61">
+        <v>9</v>
+      </c>
+      <c r="CC61">
+        <v>10</v>
+      </c>
+      <c r="CD61">
+        <v>4</v>
+      </c>
+      <c r="CE61" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF61" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG61">
+        <v>2</v>
+      </c>
+      <c r="CH61">
+        <v>4</v>
+      </c>
+      <c r="CI61">
+        <v>0</v>
+      </c>
+      <c r="CJ61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B62" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" t="s">
+        <v>107</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>53</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I62">
+        <v>3.67</v>
+      </c>
+      <c r="J62">
+        <v>3.06</v>
+      </c>
+      <c r="K62">
+        <v>19</v>
+      </c>
+      <c r="L62">
+        <v>12</v>
+      </c>
+      <c r="M62">
+        <v>9</v>
+      </c>
+      <c r="N62">
+        <v>7</v>
+      </c>
+      <c r="O62">
+        <v>3</v>
+      </c>
+      <c r="P62">
+        <v>5</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>2</v>
+      </c>
+      <c r="S62">
+        <v>447</v>
+      </c>
+      <c r="T62">
+        <v>384</v>
+      </c>
+      <c r="U62">
+        <v>13</v>
+      </c>
+      <c r="V62">
+        <v>16</v>
+      </c>
+      <c r="W62">
+        <v>3</v>
+      </c>
+      <c r="X62">
+        <v>4</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA62">
+        <v>3</v>
+      </c>
+      <c r="AB62">
+        <v>1</v>
+      </c>
+      <c r="AC62">
+        <v>7</v>
+      </c>
+      <c r="AD62">
+        <v>4</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>14</v>
+      </c>
+      <c r="AH62">
+        <v>7</v>
+      </c>
+      <c r="AI62">
+        <v>5</v>
+      </c>
+      <c r="AJ62">
+        <v>5</v>
+      </c>
+      <c r="AK62">
+        <v>2.7</v>
+      </c>
+      <c r="AL62">
+        <v>0.64</v>
+      </c>
+      <c r="AM62">
+        <v>0.18</v>
+      </c>
+      <c r="AN62">
+        <v>0.05</v>
+      </c>
+      <c r="AO62">
+        <v>2.88</v>
+      </c>
+      <c r="AP62">
+        <v>0.69</v>
+      </c>
+      <c r="AQ62">
+        <v>3.37</v>
+      </c>
+      <c r="AR62">
+        <v>3.05</v>
+      </c>
+      <c r="AS62">
+        <v>523</v>
+      </c>
+      <c r="AT62">
+        <v>461</v>
+      </c>
+      <c r="AU62">
+        <v>267</v>
+      </c>
+      <c r="AV62">
+        <v>210</v>
+      </c>
+      <c r="AW62">
+        <v>180</v>
+      </c>
+      <c r="AX62">
+        <v>174</v>
+      </c>
+      <c r="AY62">
+        <v>16</v>
+      </c>
+      <c r="AZ62">
+        <v>25</v>
+      </c>
+      <c r="BA62">
+        <v>4</v>
+      </c>
+      <c r="BB62">
+        <v>0</v>
+      </c>
+      <c r="BC62">
+        <v>18</v>
+      </c>
+      <c r="BD62">
+        <v>18</v>
+      </c>
+      <c r="BE62">
+        <v>42</v>
+      </c>
+      <c r="BF62">
+        <v>24</v>
+      </c>
+      <c r="BG62">
+        <v>1</v>
+      </c>
+      <c r="BH62">
+        <v>0</v>
+      </c>
+      <c r="BI62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK62">
+        <v>15</v>
+      </c>
+      <c r="BL62">
+        <v>14</v>
+      </c>
+      <c r="BM62">
+        <v>7</v>
+      </c>
+      <c r="BN62">
+        <v>6</v>
+      </c>
+      <c r="BO62">
+        <v>4</v>
+      </c>
+      <c r="BP62">
+        <v>8</v>
+      </c>
+      <c r="BQ62">
+        <v>27</v>
+      </c>
+      <c r="BR62">
+        <v>24</v>
+      </c>
+      <c r="BS62">
+        <v>4</v>
+      </c>
+      <c r="BT62">
+        <v>4</v>
+      </c>
+      <c r="BU62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW62">
+        <v>52</v>
+      </c>
+      <c r="BX62">
+        <v>42</v>
+      </c>
+      <c r="BY62">
+        <v>37</v>
+      </c>
+      <c r="BZ62">
+        <v>33</v>
+      </c>
+      <c r="CA62">
+        <v>15</v>
+      </c>
+      <c r="CB62">
+        <v>9</v>
+      </c>
+      <c r="CC62">
+        <v>9</v>
+      </c>
+      <c r="CD62">
+        <v>8</v>
+      </c>
+      <c r="CE62" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF62" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG62">
+        <v>3</v>
+      </c>
+      <c r="CH62">
+        <v>4</v>
+      </c>
+      <c r="CI62">
+        <v>0</v>
+      </c>
+      <c r="CJ62">
         <v>0</v>
       </c>
     </row>

--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E559E14D-908A-4677-993C-838F930B17DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB986399-57E9-45D0-9AD3-F4C312E280AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="149">
   <si>
     <t>date</t>
   </si>
@@ -484,12 +484,15 @@
   <si>
     <t>Sun 18 October, 17:15</t>
   </si>
+  <si>
+    <t>Fri 23 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,6 +522,11 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Inherit"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -540,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -559,6 +567,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,8 +905,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:CJ63"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
@@ -931,7 +942,7 @@
     <col min="84" max="84" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:88" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:88" ht="75">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1194,7 +1205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:88">
       <c r="B2" s="3" t="s">
         <v>110</v>
       </c>
@@ -1458,7 +1469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:88">
       <c r="B3" s="3" t="s">
         <v>87</v>
       </c>
@@ -1478,7 +1489,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H62" si="0">100-G3</f>
+        <f t="shared" ref="H3:H63" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -1722,7 +1733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:88">
       <c r="B4" s="3" t="s">
         <v>91</v>
       </c>
@@ -1986,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:88">
       <c r="B5" s="3" t="s">
         <v>91</v>
       </c>
@@ -2250,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:88">
       <c r="B6" s="3" t="s">
         <v>91</v>
       </c>
@@ -2514,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:88">
       <c r="B7" s="3" t="s">
         <v>91</v>
       </c>
@@ -2778,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:88">
       <c r="B8" s="3" t="s">
         <v>100</v>
       </c>
@@ -3042,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:88">
       <c r="B9" s="3" t="s">
         <v>103</v>
       </c>
@@ -3306,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:88" ht="30">
       <c r="B10" s="3" t="s">
         <v>106</v>
       </c>
@@ -3570,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:88" ht="30">
       <c r="B11" s="3" t="s">
         <v>109</v>
       </c>
@@ -3834,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:88">
       <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
@@ -4098,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:88">
       <c r="B13" s="3" t="s">
         <v>114</v>
       </c>
@@ -4362,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:88">
       <c r="B14" s="3" t="s">
         <v>114</v>
       </c>
@@ -4626,7 +4637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:88">
       <c r="B15" s="3" t="s">
         <v>114</v>
       </c>
@@ -4890,7 +4901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:88">
       <c r="B16" s="3" t="s">
         <v>114</v>
       </c>
@@ -5154,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:88">
       <c r="B17" s="3" t="s">
         <v>115</v>
       </c>
@@ -5418,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:88">
       <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
@@ -5682,7 +5693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:88">
       <c r="B19" s="3" t="s">
         <v>117</v>
       </c>
@@ -5946,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:88" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:88" ht="24" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>118</v>
       </c>
@@ -6210,7 +6221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:88">
       <c r="B21" s="3" t="s">
         <v>119</v>
       </c>
@@ -6474,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:88" ht="30">
       <c r="B22" s="3" t="s">
         <v>120</v>
       </c>
@@ -6738,7 +6749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:88" ht="27" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:88">
       <c r="B23" s="4" t="s">
         <v>121</v>
       </c>
@@ -7002,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:88" ht="27" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:88">
       <c r="B24" s="4" t="s">
         <v>122</v>
       </c>
@@ -7266,7 +7277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:88" ht="27" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:88">
       <c r="B25" s="4" t="s">
         <v>122</v>
       </c>
@@ -7530,7 +7541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:88" ht="25.5">
       <c r="B26" s="5" t="s">
         <v>123</v>
       </c>
@@ -7794,7 +7805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:88" ht="25.5">
       <c r="B27" s="5" t="s">
         <v>124</v>
       </c>
@@ -8058,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:88" ht="25.5">
       <c r="B28" s="5" t="s">
         <v>125</v>
       </c>
@@ -8322,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:88" ht="25.5">
       <c r="B29" s="5" t="s">
         <v>126</v>
       </c>
@@ -8586,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:88" ht="25.5">
       <c r="B30" s="5" t="s">
         <v>127</v>
       </c>
@@ -8850,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:88" ht="25.5">
       <c r="B31" s="5" t="s">
         <v>128</v>
       </c>
@@ -9114,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:88" ht="25.5">
       <c r="B32" s="5" t="s">
         <v>128</v>
       </c>
@@ -9378,7 +9389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:88" ht="25.5">
       <c r="B33" s="5" t="s">
         <v>128</v>
       </c>
@@ -9642,7 +9653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:88" ht="25.5">
       <c r="B34" s="5" t="s">
         <v>128</v>
       </c>
@@ -9906,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:88" ht="25.5">
       <c r="B35" s="5" t="s">
         <v>129</v>
       </c>
@@ -10170,7 +10181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:88" ht="25.5">
       <c r="B36" s="5" t="s">
         <v>130</v>
       </c>
@@ -10434,7 +10445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:88" ht="30">
       <c r="B37" s="5" t="s">
         <v>131</v>
       </c>
@@ -10698,7 +10709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:88" ht="25.5">
       <c r="B38" s="5" t="s">
         <v>132</v>
       </c>
@@ -10962,7 +10973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:88" ht="25.5">
       <c r="B39" s="5" t="s">
         <v>133</v>
       </c>
@@ -11226,7 +11237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:88" ht="25.5">
       <c r="B40" s="5" t="s">
         <v>133</v>
       </c>
@@ -11490,7 +11501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:88" ht="25.5">
       <c r="B41" s="5" t="s">
         <v>133</v>
       </c>
@@ -11754,7 +11765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:88" ht="25.5">
       <c r="B42" s="5" t="s">
         <v>133</v>
       </c>
@@ -12018,7 +12029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:88" ht="25.5">
       <c r="B43" s="5" t="s">
         <v>134</v>
       </c>
@@ -12282,7 +12293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:88" ht="25.5">
       <c r="B44" s="5" t="s">
         <v>135</v>
       </c>
@@ -12546,7 +12557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:88" ht="30">
       <c r="B45" s="5" t="s">
         <v>136</v>
       </c>
@@ -12810,7 +12821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:88">
       <c r="B46" s="6" t="s">
         <v>137</v>
       </c>
@@ -13074,7 +13085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:88">
       <c r="B47" s="5" t="s">
         <v>138</v>
       </c>
@@ -13338,7 +13349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:88">
       <c r="B48" s="5" t="s">
         <v>139</v>
       </c>
@@ -13602,7 +13613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:88">
       <c r="B49" s="5" t="s">
         <v>139</v>
       </c>
@@ -13866,7 +13877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:88">
       <c r="B50" s="5" t="s">
         <v>139</v>
       </c>
@@ -14130,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:88" ht="30">
       <c r="B51" s="5" t="s">
         <v>139</v>
       </c>
@@ -14394,7 +14405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:88" ht="25.5">
       <c r="B52" s="5" t="s">
         <v>140</v>
       </c>
@@ -14658,7 +14669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:88" ht="25.5">
       <c r="B53" s="5" t="s">
         <v>141</v>
       </c>
@@ -14922,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:88" ht="25.5">
       <c r="B54" s="5" t="s">
         <v>142</v>
       </c>
@@ -15186,7 +15197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:88">
       <c r="B55" s="6" t="s">
         <v>143</v>
       </c>
@@ -15450,7 +15461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:88" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:88" ht="30">
       <c r="B56" s="5" t="s">
         <v>144</v>
       </c>
@@ -15714,7 +15725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:88">
       <c r="B57" s="5" t="s">
         <v>145</v>
       </c>
@@ -15978,7 +15989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:88">
       <c r="B58" s="5" t="s">
         <v>145</v>
       </c>
@@ -16242,7 +16253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:88">
       <c r="B59" s="6" t="s">
         <v>146</v>
       </c>
@@ -16506,7 +16517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:88">
       <c r="B60" s="6" t="s">
         <v>147</v>
       </c>
@@ -16770,7 +16781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:88">
       <c r="B61" s="6" t="s">
         <v>147</v>
       </c>
@@ -17034,7 +17045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:88">
       <c r="B62" s="6" t="s">
         <v>147</v>
       </c>
@@ -17295,6 +17306,270 @@
         <v>0</v>
       </c>
       <c r="CJ62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:88" ht="17.25" customHeight="1">
+      <c r="B63" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D63" t="s">
+        <v>94</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>50</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="I63">
+        <v>2.48</v>
+      </c>
+      <c r="J63">
+        <v>0.44</v>
+      </c>
+      <c r="K63">
+        <v>13</v>
+      </c>
+      <c r="L63">
+        <v>9</v>
+      </c>
+      <c r="M63">
+        <v>7</v>
+      </c>
+      <c r="N63">
+        <v>2</v>
+      </c>
+      <c r="O63">
+        <v>4</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>374</v>
+      </c>
+      <c r="T63">
+        <v>370</v>
+      </c>
+      <c r="U63">
+        <v>14</v>
+      </c>
+      <c r="V63">
+        <v>15</v>
+      </c>
+      <c r="W63">
+        <v>3</v>
+      </c>
+      <c r="X63">
+        <v>7</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA63">
+        <v>4</v>
+      </c>
+      <c r="AB63">
+        <v>4</v>
+      </c>
+      <c r="AC63">
+        <v>2</v>
+      </c>
+      <c r="AD63">
+        <v>3</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>7</v>
+      </c>
+      <c r="AH63">
+        <v>4</v>
+      </c>
+      <c r="AI63">
+        <v>6</v>
+      </c>
+      <c r="AJ63">
+        <v>5</v>
+      </c>
+      <c r="AK63">
+        <v>1.55</v>
+      </c>
+      <c r="AL63">
+        <v>0.15</v>
+      </c>
+      <c r="AM63">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN63">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO63">
+        <v>1.7</v>
+      </c>
+      <c r="AP63">
+        <v>0.44</v>
+      </c>
+      <c r="AQ63">
+        <v>1.96</v>
+      </c>
+      <c r="AR63">
+        <v>1.65</v>
+      </c>
+      <c r="AS63">
+        <v>464</v>
+      </c>
+      <c r="AT63">
+        <v>453</v>
+      </c>
+      <c r="AU63">
+        <v>253</v>
+      </c>
+      <c r="AV63">
+        <v>218</v>
+      </c>
+      <c r="AW63">
+        <v>121</v>
+      </c>
+      <c r="AX63">
+        <v>152</v>
+      </c>
+      <c r="AY63">
+        <v>28</v>
+      </c>
+      <c r="AZ63">
+        <v>19</v>
+      </c>
+      <c r="BA63">
+        <v>4</v>
+      </c>
+      <c r="BB63">
+        <v>4</v>
+      </c>
+      <c r="BC63">
+        <v>21</v>
+      </c>
+      <c r="BD63">
+        <v>11</v>
+      </c>
+      <c r="BE63">
+        <v>21</v>
+      </c>
+      <c r="BF63">
+        <v>15</v>
+      </c>
+      <c r="BG63">
+        <v>1</v>
+      </c>
+      <c r="BH63">
+        <v>4</v>
+      </c>
+      <c r="BI63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK63">
+        <v>14</v>
+      </c>
+      <c r="BL63">
+        <v>20</v>
+      </c>
+      <c r="BM63">
+        <v>9</v>
+      </c>
+      <c r="BN63">
+        <v>13</v>
+      </c>
+      <c r="BO63">
+        <v>2</v>
+      </c>
+      <c r="BP63">
+        <v>2</v>
+      </c>
+      <c r="BQ63">
+        <v>19</v>
+      </c>
+      <c r="BR63">
+        <v>27</v>
+      </c>
+      <c r="BS63">
+        <v>0</v>
+      </c>
+      <c r="BT63">
+        <v>6</v>
+      </c>
+      <c r="BU63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW63">
+        <v>52</v>
+      </c>
+      <c r="BX63">
+        <v>42</v>
+      </c>
+      <c r="BY63">
+        <v>35</v>
+      </c>
+      <c r="BZ63">
+        <v>34</v>
+      </c>
+      <c r="CA63">
+        <v>17</v>
+      </c>
+      <c r="CB63">
+        <v>8</v>
+      </c>
+      <c r="CC63">
+        <v>6</v>
+      </c>
+      <c r="CD63">
+        <v>3</v>
+      </c>
+      <c r="CE63" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF63" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG63">
+        <v>3</v>
+      </c>
+      <c r="CH63">
+        <v>5</v>
+      </c>
+      <c r="CI63">
+        <v>0</v>
+      </c>
+      <c r="CJ63">
         <v>0</v>
       </c>
     </row>

--- a/Ligue 1 26-27.xlsx
+++ b/Ligue 1 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB986399-57E9-45D0-9AD3-F4C312E280AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE619573-1DAA-4685-9502-C320886D1BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="595" xr2:uid="{415BCAED-7E8B-412D-8788-FD10FF122259}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="152">
   <si>
     <t>date</t>
   </si>
@@ -487,6 +487,15 @@
   <si>
     <t>Fri 23 October, 20:45</t>
   </si>
+  <si>
+    <t>Sat 24 October, 20:45</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 17:15</t>
+  </si>
 </sst>
 </file>
 
@@ -548,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -570,6 +579,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,10 +917,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D1B5FB-6195-46B6-90CF-0D753B42CA93}">
-  <dimension ref="B1:CJ63"/>
+  <dimension ref="B1:CJ70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
@@ -1489,7 +1502,7 @@
         <v>53</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H63" si="0">100-G3</f>
+        <f t="shared" ref="H3:H70" si="0">100-G3</f>
         <v>47</v>
       </c>
       <c r="I3">
@@ -17570,6 +17583,1854 @@
         <v>0</v>
       </c>
       <c r="CJ63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:88">
+      <c r="B64" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>56</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="I64">
+        <v>1.06</v>
+      </c>
+      <c r="J64">
+        <v>0.42</v>
+      </c>
+      <c r="K64">
+        <v>9</v>
+      </c>
+      <c r="L64">
+        <v>4</v>
+      </c>
+      <c r="M64">
+        <v>3</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>478</v>
+      </c>
+      <c r="T64">
+        <v>371</v>
+      </c>
+      <c r="U64">
+        <v>17</v>
+      </c>
+      <c r="V64">
+        <v>17</v>
+      </c>
+      <c r="W64">
+        <v>6</v>
+      </c>
+      <c r="X64">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA64">
+        <v>6</v>
+      </c>
+      <c r="AB64">
+        <v>2</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>1</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>6</v>
+      </c>
+      <c r="AH64">
+        <v>4</v>
+      </c>
+      <c r="AI64">
+        <v>3</v>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>1</v>
+      </c>
+      <c r="AL64">
+        <v>0.42</v>
+      </c>
+      <c r="AM64">
+        <v>0.06</v>
+      </c>
+      <c r="AN64">
+        <v>0</v>
+      </c>
+      <c r="AO64">
+        <v>1.06</v>
+      </c>
+      <c r="AP64">
+        <v>0.42</v>
+      </c>
+      <c r="AQ64">
+        <v>1.38</v>
+      </c>
+      <c r="AR64">
+        <v>0.62</v>
+      </c>
+      <c r="AS64">
+        <v>555</v>
+      </c>
+      <c r="AT64">
+        <v>457</v>
+      </c>
+      <c r="AU64">
+        <v>268</v>
+      </c>
+      <c r="AV64">
+        <v>262</v>
+      </c>
+      <c r="AW64">
+        <v>210</v>
+      </c>
+      <c r="AX64">
+        <v>109</v>
+      </c>
+      <c r="AY64">
+        <v>26</v>
+      </c>
+      <c r="AZ64">
+        <v>14</v>
+      </c>
+      <c r="BA64">
+        <v>6</v>
+      </c>
+      <c r="BB64">
+        <v>0</v>
+      </c>
+      <c r="BC64">
+        <v>17</v>
+      </c>
+      <c r="BD64">
+        <v>18</v>
+      </c>
+      <c r="BE64">
+        <v>21</v>
+      </c>
+      <c r="BF64">
+        <v>11</v>
+      </c>
+      <c r="BG64">
+        <v>0</v>
+      </c>
+      <c r="BH64">
+        <v>1</v>
+      </c>
+      <c r="BI64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK64">
+        <v>14</v>
+      </c>
+      <c r="BL64">
+        <v>19</v>
+      </c>
+      <c r="BM64">
+        <v>13</v>
+      </c>
+      <c r="BN64">
+        <v>9</v>
+      </c>
+      <c r="BO64">
+        <v>1</v>
+      </c>
+      <c r="BP64">
+        <v>0</v>
+      </c>
+      <c r="BQ64">
+        <v>14</v>
+      </c>
+      <c r="BR64">
+        <v>39</v>
+      </c>
+      <c r="BS64">
+        <v>0</v>
+      </c>
+      <c r="BT64">
+        <v>2</v>
+      </c>
+      <c r="BU64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW64">
+        <v>45</v>
+      </c>
+      <c r="BX64">
+        <v>46</v>
+      </c>
+      <c r="BY64">
+        <v>38</v>
+      </c>
+      <c r="BZ64">
+        <v>39</v>
+      </c>
+      <c r="CA64">
+        <v>7</v>
+      </c>
+      <c r="CB64">
+        <v>7</v>
+      </c>
+      <c r="CC64">
+        <v>8</v>
+      </c>
+      <c r="CD64">
+        <v>5</v>
+      </c>
+      <c r="CE64" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF64" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG64">
+        <v>3</v>
+      </c>
+      <c r="CH64">
+        <v>3</v>
+      </c>
+      <c r="CI64">
+        <v>0</v>
+      </c>
+      <c r="CJ64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:88">
+      <c r="B65" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>64</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="I65">
+        <v>2.36</v>
+      </c>
+      <c r="J65">
+        <v>0.75</v>
+      </c>
+      <c r="K65">
+        <v>21</v>
+      </c>
+      <c r="L65">
+        <v>4</v>
+      </c>
+      <c r="M65">
+        <v>6</v>
+      </c>
+      <c r="N65">
+        <v>2</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>538</v>
+      </c>
+      <c r="T65">
+        <v>266</v>
+      </c>
+      <c r="U65">
+        <v>18</v>
+      </c>
+      <c r="V65">
+        <v>13</v>
+      </c>
+      <c r="W65">
+        <v>6</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA65">
+        <v>11</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>4</v>
+      </c>
+      <c r="AD65">
+        <v>2</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>13</v>
+      </c>
+      <c r="AH65">
+        <v>3</v>
+      </c>
+      <c r="AI65">
+        <v>8</v>
+      </c>
+      <c r="AJ65">
+        <v>1</v>
+      </c>
+      <c r="AK65">
+        <v>1.81</v>
+      </c>
+      <c r="AL65">
+        <v>0.64</v>
+      </c>
+      <c r="AM65">
+        <v>0.54</v>
+      </c>
+      <c r="AN65">
+        <v>0.11</v>
+      </c>
+      <c r="AO65">
+        <v>2.35</v>
+      </c>
+      <c r="AP65">
+        <v>0.75</v>
+      </c>
+      <c r="AQ65">
+        <v>1.41</v>
+      </c>
+      <c r="AR65">
+        <v>0.95</v>
+      </c>
+      <c r="AS65">
+        <v>603</v>
+      </c>
+      <c r="AT65">
+        <v>356</v>
+      </c>
+      <c r="AU65">
+        <v>232</v>
+      </c>
+      <c r="AV65">
+        <v>172</v>
+      </c>
+      <c r="AW65">
+        <v>306</v>
+      </c>
+      <c r="AX65">
+        <v>94</v>
+      </c>
+      <c r="AY65">
+        <v>27</v>
+      </c>
+      <c r="AZ65">
+        <v>17</v>
+      </c>
+      <c r="BA65">
+        <v>9</v>
+      </c>
+      <c r="BB65">
+        <v>0</v>
+      </c>
+      <c r="BC65">
+        <v>16</v>
+      </c>
+      <c r="BD65">
+        <v>20</v>
+      </c>
+      <c r="BE65">
+        <v>38</v>
+      </c>
+      <c r="BF65">
+        <v>7</v>
+      </c>
+      <c r="BG65">
+        <v>3</v>
+      </c>
+      <c r="BH65">
+        <v>2</v>
+      </c>
+      <c r="BI65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK65">
+        <v>13</v>
+      </c>
+      <c r="BL65">
+        <v>13</v>
+      </c>
+      <c r="BM65">
+        <v>6</v>
+      </c>
+      <c r="BN65">
+        <v>16</v>
+      </c>
+      <c r="BO65">
+        <v>2</v>
+      </c>
+      <c r="BP65">
+        <v>4</v>
+      </c>
+      <c r="BQ65">
+        <v>6</v>
+      </c>
+      <c r="BR65">
+        <v>40</v>
+      </c>
+      <c r="BS65">
+        <v>1</v>
+      </c>
+      <c r="BT65">
+        <v>5</v>
+      </c>
+      <c r="BU65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW65">
+        <v>38</v>
+      </c>
+      <c r="BX65">
+        <v>43</v>
+      </c>
+      <c r="BY65">
+        <v>31</v>
+      </c>
+      <c r="BZ65">
+        <v>34</v>
+      </c>
+      <c r="CA65">
+        <v>7</v>
+      </c>
+      <c r="CB65">
+        <v>9</v>
+      </c>
+      <c r="CC65">
+        <v>6</v>
+      </c>
+      <c r="CD65">
+        <v>3</v>
+      </c>
+      <c r="CE65" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF65" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG65">
+        <v>3</v>
+      </c>
+      <c r="CH65">
+        <v>4</v>
+      </c>
+      <c r="CI65">
+        <v>0</v>
+      </c>
+      <c r="CJ65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:88">
+      <c r="B66" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" t="s">
+        <v>95</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>48</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="I66">
+        <v>0.27</v>
+      </c>
+      <c r="J66">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K66">
+        <v>8</v>
+      </c>
+      <c r="L66">
+        <v>9</v>
+      </c>
+      <c r="M66">
+        <v>5</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>439</v>
+      </c>
+      <c r="T66">
+        <v>486</v>
+      </c>
+      <c r="U66">
+        <v>13</v>
+      </c>
+      <c r="V66">
+        <v>9</v>
+      </c>
+      <c r="W66">
+        <v>6</v>
+      </c>
+      <c r="X66">
+        <v>7</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA66">
+        <v>3</v>
+      </c>
+      <c r="AB66">
+        <v>7</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>1</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>4</v>
+      </c>
+      <c r="AH66">
+        <v>7</v>
+      </c>
+      <c r="AI66">
+        <v>4</v>
+      </c>
+      <c r="AJ66">
+        <v>2</v>
+      </c>
+      <c r="AK66">
+        <v>0.27</v>
+      </c>
+      <c r="AL66">
+        <v>0.12</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
+      <c r="AN66">
+        <v>0.44</v>
+      </c>
+      <c r="AO66">
+        <v>0.27</v>
+      </c>
+      <c r="AP66">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AQ66">
+        <v>0.73</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>493</v>
+      </c>
+      <c r="AT66">
+        <v>542</v>
+      </c>
+      <c r="AU66">
+        <v>207</v>
+      </c>
+      <c r="AV66">
+        <v>275</v>
+      </c>
+      <c r="AW66">
+        <v>232</v>
+      </c>
+      <c r="AX66">
+        <v>211</v>
+      </c>
+      <c r="AY66">
+        <v>24</v>
+      </c>
+      <c r="AZ66">
+        <v>14</v>
+      </c>
+      <c r="BA66">
+        <v>3</v>
+      </c>
+      <c r="BB66">
+        <v>10</v>
+      </c>
+      <c r="BC66">
+        <v>13</v>
+      </c>
+      <c r="BD66">
+        <v>9</v>
+      </c>
+      <c r="BE66">
+        <v>7</v>
+      </c>
+      <c r="BF66">
+        <v>23</v>
+      </c>
+      <c r="BG66">
+        <v>4</v>
+      </c>
+      <c r="BH66">
+        <v>1</v>
+      </c>
+      <c r="BI66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK66">
+        <v>10</v>
+      </c>
+      <c r="BL66">
+        <v>10</v>
+      </c>
+      <c r="BM66">
+        <v>9</v>
+      </c>
+      <c r="BN66">
+        <v>7</v>
+      </c>
+      <c r="BO66">
+        <v>2</v>
+      </c>
+      <c r="BP66">
+        <v>0</v>
+      </c>
+      <c r="BQ66">
+        <v>27</v>
+      </c>
+      <c r="BR66">
+        <v>24</v>
+      </c>
+      <c r="BS66">
+        <v>0</v>
+      </c>
+      <c r="BT66">
+        <v>5</v>
+      </c>
+      <c r="BU66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW66">
+        <v>29</v>
+      </c>
+      <c r="BX66">
+        <v>29</v>
+      </c>
+      <c r="BY66">
+        <v>19</v>
+      </c>
+      <c r="BZ66">
+        <v>23</v>
+      </c>
+      <c r="CA66">
+        <v>10</v>
+      </c>
+      <c r="CB66">
+        <v>6</v>
+      </c>
+      <c r="CC66">
+        <v>2</v>
+      </c>
+      <c r="CD66">
+        <v>3</v>
+      </c>
+      <c r="CE66" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF66" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG66">
+        <v>1</v>
+      </c>
+      <c r="CH66">
+        <v>1</v>
+      </c>
+      <c r="CI66">
+        <v>0</v>
+      </c>
+      <c r="CJ66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:88">
+      <c r="B67" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" t="s">
+        <v>89</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>59</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="I67">
+        <v>1.28</v>
+      </c>
+      <c r="J67">
+        <v>1.33</v>
+      </c>
+      <c r="K67">
+        <v>13</v>
+      </c>
+      <c r="L67">
+        <v>11</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>2</v>
+      </c>
+      <c r="P67">
+        <v>3</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <v>3</v>
+      </c>
+      <c r="S67">
+        <v>396</v>
+      </c>
+      <c r="T67">
+        <v>234</v>
+      </c>
+      <c r="U67">
+        <v>15</v>
+      </c>
+      <c r="V67">
+        <v>12</v>
+      </c>
+      <c r="W67">
+        <v>7</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA67">
+        <v>5</v>
+      </c>
+      <c r="AB67">
+        <v>9</v>
+      </c>
+      <c r="AC67">
+        <v>3</v>
+      </c>
+      <c r="AD67">
+        <v>1</v>
+      </c>
+      <c r="AE67">
+        <v>1</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>9</v>
+      </c>
+      <c r="AH67">
+        <v>8</v>
+      </c>
+      <c r="AI67">
+        <v>4</v>
+      </c>
+      <c r="AJ67">
+        <v>3</v>
+      </c>
+      <c r="AK67">
+        <v>0.99</v>
+      </c>
+      <c r="AL67">
+        <v>0.85</v>
+      </c>
+      <c r="AM67">
+        <v>0.3</v>
+      </c>
+      <c r="AN67">
+        <v>0.48</v>
+      </c>
+      <c r="AO67">
+        <v>1.28</v>
+      </c>
+      <c r="AP67">
+        <v>1.33</v>
+      </c>
+      <c r="AQ67">
+        <v>1.37</v>
+      </c>
+      <c r="AR67">
+        <v>0.62</v>
+      </c>
+      <c r="AS67">
+        <v>490</v>
+      </c>
+      <c r="AT67">
+        <v>342</v>
+      </c>
+      <c r="AU67">
+        <v>175</v>
+      </c>
+      <c r="AV67">
+        <v>155</v>
+      </c>
+      <c r="AW67">
+        <v>221</v>
+      </c>
+      <c r="AX67">
+        <v>79</v>
+      </c>
+      <c r="AY67">
+        <v>33</v>
+      </c>
+      <c r="AZ67">
+        <v>15</v>
+      </c>
+      <c r="BA67">
+        <v>3</v>
+      </c>
+      <c r="BB67">
+        <v>4</v>
+      </c>
+      <c r="BC67">
+        <v>22</v>
+      </c>
+      <c r="BD67">
+        <v>32</v>
+      </c>
+      <c r="BE67">
+        <v>22</v>
+      </c>
+      <c r="BF67">
+        <v>17</v>
+      </c>
+      <c r="BG67">
+        <v>0</v>
+      </c>
+      <c r="BH67">
+        <v>3</v>
+      </c>
+      <c r="BI67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK67">
+        <v>10</v>
+      </c>
+      <c r="BL67">
+        <v>31</v>
+      </c>
+      <c r="BM67">
+        <v>10</v>
+      </c>
+      <c r="BN67">
+        <v>17</v>
+      </c>
+      <c r="BO67">
+        <v>1</v>
+      </c>
+      <c r="BP67">
+        <v>3</v>
+      </c>
+      <c r="BQ67">
+        <v>28</v>
+      </c>
+      <c r="BR67">
+        <v>29</v>
+      </c>
+      <c r="BS67">
+        <v>1</v>
+      </c>
+      <c r="BT67">
+        <v>5</v>
+      </c>
+      <c r="BU67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW67">
+        <v>56</v>
+      </c>
+      <c r="BX67">
+        <v>74</v>
+      </c>
+      <c r="BY67">
+        <v>39</v>
+      </c>
+      <c r="BZ67">
+        <v>56</v>
+      </c>
+      <c r="CA67">
+        <v>17</v>
+      </c>
+      <c r="CB67">
+        <v>18</v>
+      </c>
+      <c r="CC67">
+        <v>17</v>
+      </c>
+      <c r="CD67">
+        <v>11</v>
+      </c>
+      <c r="CE67" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF67" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG67">
+        <v>1</v>
+      </c>
+      <c r="CH67">
+        <v>2</v>
+      </c>
+      <c r="CI67">
+        <v>0</v>
+      </c>
+      <c r="CJ67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:88">
+      <c r="B68" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" t="s">
+        <v>104</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>53</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="I68">
+        <v>1.54</v>
+      </c>
+      <c r="J68">
+        <v>3.1</v>
+      </c>
+      <c r="K68">
+        <v>11</v>
+      </c>
+      <c r="L68">
+        <v>22</v>
+      </c>
+      <c r="M68">
+        <v>5</v>
+      </c>
+      <c r="N68">
+        <v>7</v>
+      </c>
+      <c r="O68">
+        <v>3</v>
+      </c>
+      <c r="P68">
+        <v>4</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>420</v>
+      </c>
+      <c r="T68">
+        <v>338</v>
+      </c>
+      <c r="U68">
+        <v>15</v>
+      </c>
+      <c r="V68">
+        <v>11</v>
+      </c>
+      <c r="W68">
+        <v>4</v>
+      </c>
+      <c r="X68">
+        <v>3</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA68">
+        <v>4</v>
+      </c>
+      <c r="AB68">
+        <v>9</v>
+      </c>
+      <c r="AC68">
+        <v>2</v>
+      </c>
+      <c r="AD68">
+        <v>6</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>7</v>
+      </c>
+      <c r="AH68">
+        <v>14</v>
+      </c>
+      <c r="AI68">
+        <v>4</v>
+      </c>
+      <c r="AJ68">
+        <v>8</v>
+      </c>
+      <c r="AK68">
+        <v>0.36</v>
+      </c>
+      <c r="AL68">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AM68">
+        <v>1.18</v>
+      </c>
+      <c r="AN68">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO68">
+        <v>1.54</v>
+      </c>
+      <c r="AP68">
+        <v>2.31</v>
+      </c>
+      <c r="AQ68">
+        <v>3.09</v>
+      </c>
+      <c r="AR68">
+        <v>2.74</v>
+      </c>
+      <c r="AS68">
+        <v>483</v>
+      </c>
+      <c r="AT68">
+        <v>411</v>
+      </c>
+      <c r="AU68">
+        <v>185</v>
+      </c>
+      <c r="AV68">
+        <v>153</v>
+      </c>
+      <c r="AW68">
+        <v>235</v>
+      </c>
+      <c r="AX68">
+        <v>185</v>
+      </c>
+      <c r="AY68">
+        <v>22</v>
+      </c>
+      <c r="AZ68">
+        <v>27</v>
+      </c>
+      <c r="BA68">
+        <v>4</v>
+      </c>
+      <c r="BB68">
+        <v>4</v>
+      </c>
+      <c r="BC68">
+        <v>21</v>
+      </c>
+      <c r="BD68">
+        <v>22</v>
+      </c>
+      <c r="BE68">
+        <v>29</v>
+      </c>
+      <c r="BF68">
+        <v>30</v>
+      </c>
+      <c r="BG68">
+        <v>3</v>
+      </c>
+      <c r="BH68">
+        <v>1</v>
+      </c>
+      <c r="BI68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK68">
+        <v>19</v>
+      </c>
+      <c r="BL68">
+        <v>17</v>
+      </c>
+      <c r="BM68">
+        <v>14</v>
+      </c>
+      <c r="BN68">
+        <v>5</v>
+      </c>
+      <c r="BO68">
+        <v>7</v>
+      </c>
+      <c r="BP68">
+        <v>2</v>
+      </c>
+      <c r="BQ68">
+        <v>36</v>
+      </c>
+      <c r="BR68">
+        <v>23</v>
+      </c>
+      <c r="BS68">
+        <v>3</v>
+      </c>
+      <c r="BT68">
+        <v>1</v>
+      </c>
+      <c r="BU68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW68">
+        <v>47</v>
+      </c>
+      <c r="BX68">
+        <v>58</v>
+      </c>
+      <c r="BY68">
+        <v>38</v>
+      </c>
+      <c r="BZ68">
+        <v>41</v>
+      </c>
+      <c r="CA68">
+        <v>9</v>
+      </c>
+      <c r="CB68">
+        <v>17</v>
+      </c>
+      <c r="CC68">
+        <v>9</v>
+      </c>
+      <c r="CD68">
+        <v>10</v>
+      </c>
+      <c r="CE68" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF68" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG68">
+        <v>1</v>
+      </c>
+      <c r="CH68">
+        <v>3</v>
+      </c>
+      <c r="CI68">
+        <v>0</v>
+      </c>
+      <c r="CJ68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:88">
+      <c r="B69" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>46</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I69">
+        <v>1.92</v>
+      </c>
+      <c r="J69">
+        <v>0.89</v>
+      </c>
+      <c r="K69">
+        <v>15</v>
+      </c>
+      <c r="L69">
+        <v>12</v>
+      </c>
+      <c r="M69">
+        <v>5</v>
+      </c>
+      <c r="N69">
+        <v>4</v>
+      </c>
+      <c r="O69">
+        <v>2</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>398</v>
+      </c>
+      <c r="T69">
+        <v>437</v>
+      </c>
+      <c r="U69">
+        <v>10</v>
+      </c>
+      <c r="V69">
+        <v>17</v>
+      </c>
+      <c r="W69">
+        <v>2</v>
+      </c>
+      <c r="X69">
+        <v>4</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA69">
+        <v>6</v>
+      </c>
+      <c r="AB69">
+        <v>4</v>
+      </c>
+      <c r="AC69">
+        <v>4</v>
+      </c>
+      <c r="AD69">
+        <v>4</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>8</v>
+      </c>
+      <c r="AH69">
+        <v>6</v>
+      </c>
+      <c r="AI69">
+        <v>7</v>
+      </c>
+      <c r="AJ69">
+        <v>6</v>
+      </c>
+      <c r="AK69">
+        <v>1.75</v>
+      </c>
+      <c r="AL69">
+        <v>0.73</v>
+      </c>
+      <c r="AM69">
+        <v>0.16</v>
+      </c>
+      <c r="AN69">
+        <v>0.15</v>
+      </c>
+      <c r="AO69">
+        <v>1.92</v>
+      </c>
+      <c r="AP69">
+        <v>0.89</v>
+      </c>
+      <c r="AQ69">
+        <v>2.68</v>
+      </c>
+      <c r="AR69">
+        <v>0.16</v>
+      </c>
+      <c r="AS69">
+        <v>476</v>
+      </c>
+      <c r="AT69">
+        <v>539</v>
+      </c>
+      <c r="AU69">
+        <v>265</v>
+      </c>
+      <c r="AV69">
+        <v>251</v>
+      </c>
+      <c r="AW69">
+        <v>133</v>
+      </c>
+      <c r="AX69">
+        <v>186</v>
+      </c>
+      <c r="AY69">
+        <v>21</v>
+      </c>
+      <c r="AZ69">
+        <v>21</v>
+      </c>
+      <c r="BA69">
+        <v>4</v>
+      </c>
+      <c r="BB69">
+        <v>4</v>
+      </c>
+      <c r="BC69">
+        <v>23</v>
+      </c>
+      <c r="BD69">
+        <v>25</v>
+      </c>
+      <c r="BE69">
+        <v>27</v>
+      </c>
+      <c r="BF69">
+        <v>26</v>
+      </c>
+      <c r="BG69">
+        <v>1</v>
+      </c>
+      <c r="BH69">
+        <v>0</v>
+      </c>
+      <c r="BI69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK69">
+        <v>23</v>
+      </c>
+      <c r="BL69">
+        <v>15</v>
+      </c>
+      <c r="BM69">
+        <v>19</v>
+      </c>
+      <c r="BN69">
+        <v>7</v>
+      </c>
+      <c r="BO69">
+        <v>5</v>
+      </c>
+      <c r="BP69">
+        <v>4</v>
+      </c>
+      <c r="BQ69">
+        <v>32</v>
+      </c>
+      <c r="BR69">
+        <v>6</v>
+      </c>
+      <c r="BS69">
+        <v>3</v>
+      </c>
+      <c r="BT69">
+        <v>2</v>
+      </c>
+      <c r="BU69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW69">
+        <v>54</v>
+      </c>
+      <c r="BX69">
+        <v>50</v>
+      </c>
+      <c r="BY69">
+        <v>40</v>
+      </c>
+      <c r="BZ69">
+        <v>35</v>
+      </c>
+      <c r="CA69">
+        <v>14</v>
+      </c>
+      <c r="CB69">
+        <v>15</v>
+      </c>
+      <c r="CC69">
+        <v>4</v>
+      </c>
+      <c r="CD69">
+        <v>13</v>
+      </c>
+      <c r="CE69" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF69" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG69">
+        <v>1</v>
+      </c>
+      <c r="CH69">
+        <v>3</v>
+      </c>
+      <c r="CI69">
+        <v>0</v>
+      </c>
+      <c r="CJ69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:88">
+      <c r="B70" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>63</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="I70">
+        <v>0.84</v>
+      </c>
+      <c r="J70">
+        <v>0.39</v>
+      </c>
+      <c r="K70">
+        <v>7</v>
+      </c>
+      <c r="L70">
+        <v>8</v>
+      </c>
+      <c r="M70">
+        <v>3</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>531</v>
+      </c>
+      <c r="T70">
+        <v>275</v>
+      </c>
+      <c r="U70">
+        <v>19</v>
+      </c>
+      <c r="V70">
+        <v>14</v>
+      </c>
+      <c r="W70">
+        <v>4</v>
+      </c>
+      <c r="X70">
+        <v>2</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA70">
+        <v>2</v>
+      </c>
+      <c r="AB70">
+        <v>2</v>
+      </c>
+      <c r="AC70">
+        <v>2</v>
+      </c>
+      <c r="AD70">
+        <v>6</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>6</v>
+      </c>
+      <c r="AH70">
+        <v>2</v>
+      </c>
+      <c r="AI70">
+        <v>1</v>
+      </c>
+      <c r="AJ70">
+        <v>6</v>
+      </c>
+      <c r="AK70">
+        <v>0.83</v>
+      </c>
+      <c r="AL70">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AM70">
+        <v>0.01</v>
+      </c>
+      <c r="AN70">
+        <v>0.11</v>
+      </c>
+      <c r="AO70">
+        <v>0.84</v>
+      </c>
+      <c r="AP70">
+        <v>0.39</v>
+      </c>
+      <c r="AQ70">
+        <v>0.68</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>597</v>
+      </c>
+      <c r="AT70">
+        <v>344</v>
+      </c>
+      <c r="AU70">
+        <v>294</v>
+      </c>
+      <c r="AV70">
+        <v>137</v>
+      </c>
+      <c r="AW70">
+        <v>237</v>
+      </c>
+      <c r="AX70">
+        <v>138</v>
+      </c>
+      <c r="AY70">
+        <v>16</v>
+      </c>
+      <c r="AZ70">
+        <v>31</v>
+      </c>
+      <c r="BA70">
+        <v>3</v>
+      </c>
+      <c r="BB70">
+        <v>3</v>
+      </c>
+      <c r="BC70">
+        <v>17</v>
+      </c>
+      <c r="BD70">
+        <v>16</v>
+      </c>
+      <c r="BE70">
+        <v>15</v>
+      </c>
+      <c r="BF70">
+        <v>18</v>
+      </c>
+      <c r="BG70">
+        <v>1</v>
+      </c>
+      <c r="BH70">
+        <v>0</v>
+      </c>
+      <c r="BI70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK70">
+        <v>9</v>
+      </c>
+      <c r="BL70">
+        <v>23</v>
+      </c>
+      <c r="BM70">
+        <v>6</v>
+      </c>
+      <c r="BN70">
+        <v>9</v>
+      </c>
+      <c r="BO70">
+        <v>6</v>
+      </c>
+      <c r="BP70">
+        <v>2</v>
+      </c>
+      <c r="BQ70">
+        <v>15</v>
+      </c>
+      <c r="BR70">
+        <v>14</v>
+      </c>
+      <c r="BS70">
+        <v>0</v>
+      </c>
+      <c r="BT70">
+        <v>3</v>
+      </c>
+      <c r="BU70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW70">
+        <v>38</v>
+      </c>
+      <c r="BX70">
+        <v>55</v>
+      </c>
+      <c r="BY70">
+        <v>26</v>
+      </c>
+      <c r="BZ70">
+        <v>46</v>
+      </c>
+      <c r="CA70">
+        <v>12</v>
+      </c>
+      <c r="CB70">
+        <v>9</v>
+      </c>
+      <c r="CC70">
+        <v>4</v>
+      </c>
+      <c r="CD70">
+        <v>6</v>
+      </c>
+      <c r="CE70" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF70" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG70">
+        <v>7</v>
+      </c>
+      <c r="CH70">
+        <v>2</v>
+      </c>
+      <c r="CI70">
+        <v>0</v>
+      </c>
+      <c r="CJ70">
         <v>0</v>
       </c>
     </row>
